--- a/data/source/weekly/cs-en-us-023pct.xlsx
+++ b/data/source/weekly/cs-en-us-023pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">6</t>
+      <t xml:space="preserve">7</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/2/2026</t>
+      <t xml:space="preserve">2/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/8/2026</t>
+      <t xml:space="preserve">2/15/2026</t>
     </r>
   </si>
   <si>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
+        <v>1</v>
+      </c>
+      <c r="D16" s="14">
         <v>4</v>
       </c>
-      <c r="D16" s="14">
-        <v>5</v>
-      </c>
       <c r="E16" s="15">
-        <v>-20</v>
+        <v>-75</v>
       </c>
       <c r="F16" s="14">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G16" s="14">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H16" s="15">
-        <v>-37.5</v>
+        <v>-47.619047619047</v>
       </c>
       <c r="I16" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J16" s="14">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="K16" s="15">
-        <v>-41.379310344827</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="L16" s="15">
-        <v>-22.727272727272</v>
+        <v>-28</v>
       </c>
       <c r="M16" s="15">
-        <v>-34.615384615384</v>
+        <v>-40</v>
       </c>
       <c r="N16" s="15">
-        <v>-77.922077922077</v>
+        <v>-80.434782608695</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D17" s="14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E17" s="15">
-        <v>-28.571428571428</v>
+        <v>-60</v>
       </c>
       <c r="F17" s="14">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G17" s="14">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H17" s="15">
-        <v>10</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I17" s="14">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="J17" s="14">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="K17" s="15">
-        <v>-30</v>
+        <v>-34</v>
       </c>
       <c r="L17" s="15">
-        <v>-31.707317073170</v>
+        <v>-31.25</v>
       </c>
       <c r="M17" s="15">
-        <v>86.666666666666</v>
+        <v>83.333333333333</v>
       </c>
       <c r="N17" s="15">
-        <v>-54.098360655737</v>
+        <v>-51.470588235294</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>21</v>
+      <c r="C18" s="14">
+        <v>1</v>
+      </c>
+      <c r="D18" s="14">
+        <v>2</v>
+      </c>
+      <c r="E18" s="15">
+        <v>-50</v>
       </c>
       <c r="F18" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G18" s="14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H18" s="15">
-        <v>-40</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="I18" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J18" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K18" s="15">
-        <v>-16.666666666666</v>
+        <v>-21.428571428571</v>
       </c>
       <c r="L18" s="15">
-        <v>-23.076923076923</v>
+        <v>-26.666666666666</v>
       </c>
       <c r="M18" s="15">
-        <v>11.111111111111</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="N18" s="15">
-        <v>-74.358974358974</v>
+        <v>-76.595744680851</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D19" s="14">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E19" s="15">
-        <v>20</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="F19" s="14">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G19" s="14">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H19" s="15">
-        <v>-30.303030303030</v>
+        <v>-38.235294117647</v>
       </c>
       <c r="I19" s="14">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="J19" s="14">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="K19" s="15">
-        <v>-18.604651162790</v>
+        <v>-17.307692307692</v>
       </c>
       <c r="L19" s="15">
-        <v>-10.256410256410</v>
+        <v>-6.521739130434</v>
       </c>
       <c r="M19" s="15">
-        <v>52.173913043478</v>
+        <v>53.571428571428</v>
       </c>
       <c r="N19" s="15">
-        <v>-53.333333333333</v>
+        <v>-52.222222222222</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D20" s="14">
         <v>1</v>
       </c>
       <c r="E20" s="15">
+        <v>100</v>
+      </c>
+      <c r="F20" s="14">
+        <v>3</v>
+      </c>
+      <c r="G20" s="14">
+        <v>3</v>
+      </c>
+      <c r="H20" s="15">
         <v>0</v>
       </c>
-      <c r="F20" s="14">
+      <c r="I20" s="14">
+        <v>7</v>
+      </c>
+      <c r="J20" s="14">
         <v>4</v>
       </c>
-      <c r="G20" s="14">
-        <v>2</v>
-      </c>
-      <c r="H20" s="15">
-        <v>100</v>
-      </c>
-      <c r="I20" s="14">
-        <v>5</v>
-      </c>
-      <c r="J20" s="14">
-        <v>3</v>
-      </c>
       <c r="K20" s="15">
-        <v>66.666666666666</v>
+        <v>75</v>
       </c>
       <c r="L20" s="15">
-        <v>0</v>
+        <v>16.666666666666</v>
       </c>
       <c r="M20" s="15">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="N20" s="15">
-        <v>-87.804878048780</v>
+        <v>-85.714285714285</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,37 +1142,37 @@
         <v>16</v>
       </c>
       <c r="D21" s="17">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="E21" s="18">
-        <v>-11.111111111111</v>
+        <v>-38.461538461538</v>
       </c>
       <c r="F21" s="17">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="G21" s="17">
         <v>90</v>
       </c>
       <c r="H21" s="18">
-        <v>-22.222222222222</v>
+        <v>-34.444444444444</v>
       </c>
       <c r="I21" s="17">
-        <v>95</v>
+        <v>112</v>
       </c>
       <c r="J21" s="17">
-        <v>130</v>
+        <v>156</v>
       </c>
       <c r="K21" s="18">
-        <v>-26.923076923076</v>
+        <v>-28.205128205128</v>
       </c>
       <c r="L21" s="18">
-        <v>-22.131147540983</v>
+        <v>-21.126760563380</v>
       </c>
       <c r="M21" s="18">
-        <v>21.794871794871</v>
+        <v>20.430107526881</v>
       </c>
       <c r="N21" s="18">
-        <v>-69.055374592833</v>
+        <v>-68.975069252077</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D23" s="14">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E23" s="15">
-        <v>0</v>
+        <v>-80</v>
       </c>
       <c r="F23" s="14">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="G23" s="14">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H23" s="15">
-        <v>-3.448275862068</v>
+        <v>-35.483870967741</v>
       </c>
       <c r="I23" s="14">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="J23" s="14">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="K23" s="15">
-        <v>-2.777777777777</v>
+        <v>-17.391304347826</v>
       </c>
       <c r="L23" s="15">
-        <v>-7.894736842105</v>
+        <v>-13.636363636363</v>
       </c>
       <c r="M23" s="15">
-        <v>105.882352941176</v>
+        <v>72.727272727272</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D24" s="14">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E24" s="15">
-        <v>-35.714285714285</v>
+        <v>9.523809523809</v>
       </c>
       <c r="F24" s="14">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="G24" s="14">
         <v>87</v>
       </c>
       <c r="H24" s="15">
-        <v>-20.689655172413</v>
+        <v>-10.344827586206</v>
       </c>
       <c r="I24" s="14">
-        <v>93</v>
+        <v>114</v>
       </c>
       <c r="J24" s="14">
-        <v>101</v>
+        <v>122</v>
       </c>
       <c r="K24" s="15">
-        <v>-7.920792079207</v>
+        <v>-6.557377049180</v>
       </c>
       <c r="L24" s="15">
-        <v>16.25</v>
+        <v>25.274725274725</v>
       </c>
       <c r="M24" s="15">
-        <v>34.782608695652</v>
+        <v>37.349397590361</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D25" s="14">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E25" s="15">
-        <v>100</v>
+        <v>-58.333333333333</v>
       </c>
       <c r="F25" s="14">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G25" s="14">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="H25" s="15">
-        <v>40</v>
+        <v>16.129032258064</v>
       </c>
       <c r="I25" s="14">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="J25" s="14">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="K25" s="15">
-        <v>59.259259259259</v>
+        <v>23.076923076923</v>
       </c>
       <c r="L25" s="15">
-        <v>290.909090909091</v>
+        <v>269.230769230769</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D26" s="14">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E26" s="15">
-        <v>220</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="F26" s="14">
         <v>41</v>
       </c>
       <c r="G26" s="14">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H26" s="15">
-        <v>13.888888888888</v>
+        <v>7.894736842105</v>
       </c>
       <c r="I26" s="14">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="J26" s="14">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="K26" s="15">
-        <v>32.608695652173</v>
+        <v>25.454545454545</v>
       </c>
       <c r="L26" s="15">
-        <v>12.962962962963</v>
+        <v>1.470588235294</v>
       </c>
       <c r="M26" s="15">
-        <v>-3.174603174603</v>
+        <v>1.470588235294</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1435,25 +1435,25 @@
         <v>21</v>
       </c>
       <c r="F28" s="14">
+        <v>5</v>
+      </c>
+      <c r="G28" s="14">
         <v>4</v>
       </c>
-      <c r="G28" s="14">
-        <v>5</v>
-      </c>
       <c r="H28" s="15">
-        <v>-20</v>
+        <v>25</v>
       </c>
       <c r="I28" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J28" s="14">
         <v>5</v>
       </c>
       <c r="K28" s="15">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="L28" s="15">
-        <v>33.333333333333</v>
+        <v>50</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1500,7 +1500,7 @@
         <v>-50</v>
       </c>
       <c r="N29" s="15">
-        <v>-94.444444444444</v>
+        <v>-94.736842105263</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1541,7 +1541,7 @@
         <v>-50</v>
       </c>
       <c r="N30" s="15">
-        <v>-94.117647058823</v>
+        <v>-94.444444444444</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-023pct.xlsx
+++ b/data/source/weekly/cs-en-us-023pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">7</t>
+      <t xml:space="preserve">8</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/9/2026</t>
+      <t xml:space="preserve">2/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/15/2026</t>
+      <t xml:space="preserve">2/22/2026</t>
     </r>
   </si>
   <si>
@@ -901,32 +901,32 @@
       <c r="E15" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F15" s="13" t="s">
-        <v>20</v>
+      <c r="F15" s="14">
+        <v>1</v>
       </c>
       <c r="G15" s="14">
         <v>1</v>
       </c>
       <c r="H15" s="15">
-        <v>-100</v>
-      </c>
-      <c r="I15" s="13" t="s">
-        <v>20</v>
+        <v>0</v>
+      </c>
+      <c r="I15" s="14">
+        <v>1</v>
       </c>
       <c r="J15" s="14">
         <v>2</v>
       </c>
       <c r="K15" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="L15" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M15" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="N15" s="15">
-        <v>-100</v>
+        <v>-92.307692307692</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D16" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E16" s="15">
-        <v>-75</v>
+        <v>50</v>
       </c>
       <c r="F16" s="14">
         <v>11</v>
       </c>
       <c r="G16" s="14">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H16" s="15">
-        <v>-47.619047619047</v>
+        <v>-38.888888888888</v>
       </c>
       <c r="I16" s="14">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J16" s="14">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K16" s="15">
-        <v>-45.454545454545</v>
+        <v>-40</v>
       </c>
       <c r="L16" s="15">
-        <v>-28</v>
+        <v>-27.586206896551</v>
       </c>
       <c r="M16" s="15">
-        <v>-40</v>
+        <v>-38.235294117647</v>
       </c>
       <c r="N16" s="15">
-        <v>-80.434782608695</v>
+        <v>-80.373831775700</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D17" s="14">
         <v>10</v>
       </c>
       <c r="E17" s="15">
-        <v>-60</v>
+        <v>-50</v>
       </c>
       <c r="F17" s="14">
         <v>20</v>
       </c>
       <c r="G17" s="14">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H17" s="15">
-        <v>-16.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I17" s="14">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="J17" s="14">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="K17" s="15">
-        <v>-34</v>
+        <v>-36.666666666666</v>
       </c>
       <c r="L17" s="15">
-        <v>-31.25</v>
+        <v>-26.923076923076</v>
       </c>
       <c r="M17" s="15">
-        <v>83.333333333333</v>
+        <v>100</v>
       </c>
       <c r="N17" s="15">
-        <v>-51.470588235294</v>
+        <v>-50.649350649350</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,37 +1019,37 @@
         <v>1</v>
       </c>
       <c r="D18" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E18" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="F18" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G18" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H18" s="15">
-        <v>-42.857142857142</v>
+        <v>-40</v>
       </c>
       <c r="I18" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J18" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K18" s="15">
-        <v>-21.428571428571</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="L18" s="15">
-        <v>-26.666666666666</v>
+        <v>-31.578947368421</v>
       </c>
       <c r="M18" s="15">
-        <v>-8.333333333333</v>
+        <v>8.333333333333</v>
       </c>
       <c r="N18" s="15">
-        <v>-76.595744680851</v>
+        <v>-79.032258064516</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,54 +1057,54 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D19" s="14">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E19" s="15">
-        <v>-11.111111111111</v>
+        <v>0</v>
       </c>
       <c r="F19" s="14">
         <v>21</v>
       </c>
       <c r="G19" s="14">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="H19" s="15">
-        <v>-38.235294117647</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="I19" s="14">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="J19" s="14">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="K19" s="15">
-        <v>-17.307692307692</v>
+        <v>-12.5</v>
       </c>
       <c r="L19" s="15">
-        <v>-6.521739130434</v>
+        <v>-9.259259259259</v>
       </c>
       <c r="M19" s="15">
-        <v>53.571428571428</v>
+        <v>58.064516129032</v>
       </c>
       <c r="N19" s="15">
-        <v>-52.222222222222</v>
+        <v>-49.484536082474</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="14">
-        <v>2</v>
+      <c r="C20" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D20" s="14">
         <v>1</v>
       </c>
       <c r="E20" s="15">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="F20" s="14">
         <v>3</v>
@@ -1119,19 +1119,19 @@
         <v>7</v>
       </c>
       <c r="J20" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K20" s="15">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="L20" s="15">
-        <v>16.666666666666</v>
+        <v>0</v>
       </c>
       <c r="M20" s="15">
         <v>250</v>
       </c>
       <c r="N20" s="15">
-        <v>-85.714285714285</v>
+        <v>-87.719298245614</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D21" s="17">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="E21" s="18">
-        <v>-38.461538461538</v>
+        <v>-27.777777777777</v>
       </c>
       <c r="F21" s="17">
         <v>59</v>
       </c>
       <c r="G21" s="17">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="H21" s="18">
-        <v>-34.444444444444</v>
+        <v>-29.761904761904</v>
       </c>
       <c r="I21" s="17">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="J21" s="17">
-        <v>156</v>
+        <v>174</v>
       </c>
       <c r="K21" s="18">
-        <v>-28.205128205128</v>
+        <v>-25.862068965517</v>
       </c>
       <c r="L21" s="18">
-        <v>-21.126760563380</v>
+        <v>-20.858895705521</v>
       </c>
       <c r="M21" s="18">
-        <v>20.430107526881</v>
+        <v>27.722772277227</v>
       </c>
       <c r="N21" s="18">
-        <v>-68.975069252077</v>
+        <v>-69.138755980861</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1191,11 +1191,11 @@
       <c r="F22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G22" s="14">
-        <v>1</v>
-      </c>
-      <c r="H22" s="15">
-        <v>-100</v>
+      <c r="G22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I22" s="14">
         <v>1</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D23" s="14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E23" s="15">
-        <v>-80</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="F23" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G23" s="14">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H23" s="15">
-        <v>-35.483870967741</v>
+        <v>-34.375</v>
       </c>
       <c r="I23" s="14">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="J23" s="14">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="K23" s="15">
-        <v>-17.391304347826</v>
+        <v>-13.207547169811</v>
       </c>
       <c r="L23" s="15">
-        <v>-13.636363636363</v>
+        <v>-9.803921568627</v>
       </c>
       <c r="M23" s="15">
-        <v>72.727272727272</v>
+        <v>70.370370370370</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D24" s="14">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E24" s="15">
-        <v>9.523809523809</v>
+        <v>-12</v>
       </c>
       <c r="F24" s="14">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G24" s="14">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="H24" s="15">
-        <v>-10.344827586206</v>
+        <v>-20.202020202020</v>
       </c>
       <c r="I24" s="14">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="J24" s="14">
-        <v>122</v>
+        <v>147</v>
       </c>
       <c r="K24" s="15">
-        <v>-6.557377049180</v>
+        <v>-10.884353741496</v>
       </c>
       <c r="L24" s="15">
-        <v>25.274725274725</v>
+        <v>25.961538461538</v>
       </c>
       <c r="M24" s="15">
-        <v>37.349397590361</v>
+        <v>47.191011235955</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D25" s="14">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E25" s="15">
-        <v>-58.333333333333</v>
+        <v>-62.5</v>
       </c>
       <c r="F25" s="14">
+        <v>33</v>
+      </c>
+      <c r="G25" s="14">
         <v>36</v>
       </c>
-      <c r="G25" s="14">
-        <v>31</v>
-      </c>
       <c r="H25" s="15">
-        <v>16.129032258064</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="I25" s="14">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="J25" s="14">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="K25" s="15">
-        <v>23.076923076923</v>
+        <v>8.510638297872</v>
       </c>
       <c r="L25" s="15">
-        <v>269.230769230769</v>
+        <v>264.285714285714</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D26" s="14">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E26" s="15">
-        <v>-11.111111111111</v>
+        <v>0</v>
       </c>
       <c r="F26" s="14">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G26" s="14">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H26" s="15">
-        <v>7.894736842105</v>
+        <v>22.222222222222</v>
       </c>
       <c r="I26" s="14">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="J26" s="14">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="K26" s="15">
-        <v>25.454545454545</v>
+        <v>20.895522388059</v>
       </c>
       <c r="L26" s="15">
-        <v>1.470588235294</v>
+        <v>-3.571428571428</v>
       </c>
       <c r="M26" s="15">
-        <v>1.470588235294</v>
+        <v>3.846153846153</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1393,26 +1393,26 @@
       <c r="E27" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F27" s="13" t="s">
-        <v>20</v>
+      <c r="F27" s="14">
+        <v>1</v>
       </c>
       <c r="G27" s="14">
         <v>1</v>
       </c>
       <c r="H27" s="15">
-        <v>-100</v>
-      </c>
-      <c r="I27" s="13" t="s">
-        <v>20</v>
+        <v>0</v>
+      </c>
+      <c r="I27" s="14">
+        <v>1</v>
       </c>
       <c r="J27" s="14">
         <v>2</v>
       </c>
       <c r="K27" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="L27" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1428,32 +1428,32 @@
       <c r="C28" s="14">
         <v>1</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="D28" s="14">
+        <v>1</v>
+      </c>
+      <c r="E28" s="15">
+        <v>0</v>
       </c>
       <c r="F28" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G28" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H28" s="15">
+        <v>0</v>
+      </c>
+      <c r="I28" s="14">
+        <v>10</v>
+      </c>
+      <c r="J28" s="14">
+        <v>6</v>
+      </c>
+      <c r="K28" s="15">
+        <v>66.666666666666</v>
+      </c>
+      <c r="L28" s="15">
         <v>25</v>
-      </c>
-      <c r="I28" s="14">
-        <v>9</v>
-      </c>
-      <c r="J28" s="14">
-        <v>5</v>
-      </c>
-      <c r="K28" s="15">
-        <v>80</v>
-      </c>
-      <c r="L28" s="15">
-        <v>50</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1497,10 +1497,10 @@
         <v>0</v>
       </c>
       <c r="M29" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="N29" s="15">
-        <v>-94.736842105263</v>
+        <v>-95.652173913043</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1538,10 +1538,10 @@
         <v>0</v>
       </c>
       <c r="M30" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="N30" s="15">
-        <v>-94.444444444444</v>
+        <v>-95.454545454545</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-023pct.xlsx
+++ b/data/source/weekly/cs-en-us-023pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">8</t>
+      <t xml:space="preserve">9</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/16/2026</t>
+      <t xml:space="preserve">2/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/22/2026</t>
+      <t xml:space="preserve">3/1/2026</t>
     </r>
   </si>
   <si>
@@ -892,8 +892,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="14">
+        <v>1</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -902,31 +902,31 @@
         <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>1</v>
-      </c>
-      <c r="G15" s="14">
-        <v>1</v>
-      </c>
-      <c r="H15" s="15">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="G15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I15" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J15" s="14">
         <v>2</v>
       </c>
       <c r="K15" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="L15" s="15">
+        <v>100</v>
+      </c>
+      <c r="M15" s="15">
         <v>0</v>
       </c>
-      <c r="M15" s="15">
-        <v>-50</v>
-      </c>
       <c r="N15" s="15">
-        <v>-92.307692307692</v>
+        <v>-85.714285714285</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D16" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E16" s="15">
-        <v>50</v>
+        <v>-60</v>
       </c>
       <c r="F16" s="14">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G16" s="14">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H16" s="15">
-        <v>-38.888888888888</v>
+        <v>-37.5</v>
       </c>
       <c r="I16" s="14">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J16" s="14">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="K16" s="15">
-        <v>-40</v>
+        <v>-42.5</v>
       </c>
       <c r="L16" s="15">
-        <v>-27.586206896551</v>
+        <v>-32.352941176470</v>
       </c>
       <c r="M16" s="15">
-        <v>-38.235294117647</v>
+        <v>-41.025641025641</v>
       </c>
       <c r="N16" s="15">
-        <v>-80.373831775700</v>
+        <v>-80.341880341880</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,78 +978,78 @@
         <v>5</v>
       </c>
       <c r="D17" s="14">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E17" s="15">
-        <v>-50</v>
+        <v>-64.285714285714</v>
       </c>
       <c r="F17" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G17" s="14">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="H17" s="15">
-        <v>-33.333333333333</v>
+        <v>-48.780487804878</v>
       </c>
       <c r="I17" s="14">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="J17" s="14">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="K17" s="15">
-        <v>-36.666666666666</v>
+        <v>-40.540540540540</v>
       </c>
       <c r="L17" s="15">
-        <v>-26.923076923076</v>
+        <v>-24.137931034482</v>
       </c>
       <c r="M17" s="15">
-        <v>100</v>
+        <v>91.304347826087</v>
       </c>
       <c r="N17" s="15">
-        <v>-50.649350649350</v>
+        <v>-49.425287356321</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="14">
-        <v>1</v>
+      <c r="C18" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D18" s="14">
         <v>1</v>
       </c>
       <c r="E18" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F18" s="14">
         <v>3</v>
       </c>
       <c r="G18" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H18" s="15">
-        <v>-40</v>
+        <v>-25</v>
       </c>
       <c r="I18" s="14">
         <v>13</v>
       </c>
       <c r="J18" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K18" s="15">
-        <v>-13.333333333333</v>
+        <v>-18.75</v>
       </c>
       <c r="L18" s="15">
-        <v>-31.578947368421</v>
+        <v>-48</v>
       </c>
       <c r="M18" s="15">
-        <v>8.333333333333</v>
+        <v>0</v>
       </c>
       <c r="N18" s="15">
-        <v>-79.032258064516</v>
+        <v>-81.428571428571</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D19" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E19" s="15">
-        <v>0</v>
+        <v>14.285714285714</v>
       </c>
       <c r="F19" s="14">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="G19" s="14">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H19" s="15">
-        <v>-22.222222222222</v>
+        <v>12</v>
       </c>
       <c r="I19" s="14">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="J19" s="14">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="K19" s="15">
-        <v>-12.5</v>
+        <v>-7.936507936507</v>
       </c>
       <c r="L19" s="15">
-        <v>-9.259259259259</v>
+        <v>-7.936507936507</v>
       </c>
       <c r="M19" s="15">
-        <v>58.064516129032</v>
+        <v>81.25</v>
       </c>
       <c r="N19" s="15">
-        <v>-49.484536082474</v>
+        <v>-44.230769230769</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,7 +1101,7 @@
         <v>20</v>
       </c>
       <c r="D20" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E20" s="15">
         <v>-100</v>
@@ -1110,28 +1110,28 @@
         <v>3</v>
       </c>
       <c r="G20" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H20" s="15">
-        <v>0</v>
+        <v>-40</v>
       </c>
       <c r="I20" s="14">
         <v>7</v>
       </c>
       <c r="J20" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K20" s="15">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L20" s="15">
-        <v>0</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="M20" s="15">
         <v>250</v>
       </c>
       <c r="N20" s="15">
-        <v>-87.719298245614</v>
+        <v>-88.135593220339</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D21" s="17">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="E21" s="18">
-        <v>-27.777777777777</v>
+        <v>-44.827586206896</v>
       </c>
       <c r="F21" s="17">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="G21" s="17">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="H21" s="18">
-        <v>-29.761904761904</v>
+        <v>-26.373626373626</v>
       </c>
       <c r="I21" s="17">
-        <v>129</v>
+        <v>147</v>
       </c>
       <c r="J21" s="17">
-        <v>174</v>
+        <v>203</v>
       </c>
       <c r="K21" s="18">
-        <v>-25.862068965517</v>
+        <v>-27.586206896551</v>
       </c>
       <c r="L21" s="18">
-        <v>-20.858895705521</v>
+        <v>-23.036649214659</v>
       </c>
       <c r="M21" s="18">
-        <v>27.722772277227</v>
+        <v>31.25</v>
       </c>
       <c r="N21" s="18">
-        <v>-69.138755980861</v>
+        <v>-67.763157894736</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D23" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E23" s="15">
-        <v>-42.857142857142</v>
+        <v>-62.5</v>
       </c>
       <c r="F23" s="14">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G23" s="14">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H23" s="15">
-        <v>-34.375</v>
+        <v>-36.666666666666</v>
       </c>
       <c r="I23" s="14">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="J23" s="14">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="K23" s="15">
-        <v>-13.207547169811</v>
+        <v>-19.672131147541</v>
       </c>
       <c r="L23" s="15">
-        <v>-9.803921568627</v>
+        <v>-16.949152542372</v>
       </c>
       <c r="M23" s="15">
-        <v>70.370370370370</v>
+        <v>63.333333333333</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
+        <v>14</v>
+      </c>
+      <c r="D24" s="14">
         <v>22</v>
       </c>
-      <c r="D24" s="14">
-        <v>25</v>
-      </c>
       <c r="E24" s="15">
-        <v>-12</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="F24" s="14">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="G24" s="14">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="H24" s="15">
-        <v>-20.202020202020</v>
+        <v>-29.166666666666</v>
       </c>
       <c r="I24" s="14">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="J24" s="14">
-        <v>147</v>
+        <v>169</v>
       </c>
       <c r="K24" s="15">
-        <v>-10.884353741496</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="L24" s="15">
-        <v>25.961538461538</v>
+        <v>20.168067226890</v>
       </c>
       <c r="M24" s="15">
-        <v>47.191011235955</v>
+        <v>45.918367346938</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D25" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E25" s="15">
-        <v>-62.5</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F25" s="14">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G25" s="14">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H25" s="15">
-        <v>-8.333333333333</v>
+        <v>-29.411764705882</v>
       </c>
       <c r="I25" s="14">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="J25" s="14">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="K25" s="15">
-        <v>8.510638297872</v>
+        <v>1.785714285714</v>
       </c>
       <c r="L25" s="15">
-        <v>264.285714285714</v>
+        <v>200</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D26" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E26" s="15">
-        <v>0</v>
+        <v>-38.461538461538</v>
       </c>
       <c r="F26" s="14">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G26" s="14">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H26" s="15">
-        <v>22.222222222222</v>
+        <v>10.256410256410</v>
       </c>
       <c r="I26" s="14">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="J26" s="14">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="K26" s="15">
-        <v>20.895522388059</v>
+        <v>10</v>
       </c>
       <c r="L26" s="15">
-        <v>-3.571428571428</v>
+        <v>-10.204081632653</v>
       </c>
       <c r="M26" s="15">
-        <v>3.846153846153</v>
+        <v>-2.222222222222</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="14">
+        <v>1</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1394,25 +1394,25 @@
         <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>1</v>
-      </c>
-      <c r="G27" s="14">
-        <v>1</v>
-      </c>
-      <c r="H27" s="15">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="G27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I27" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J27" s="14">
         <v>2</v>
       </c>
       <c r="K27" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="L27" s="15">
-        <v>-50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,23 +1425,23 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
-        <v>1</v>
-      </c>
-      <c r="D28" s="14">
-        <v>1</v>
-      </c>
-      <c r="E28" s="15">
-        <v>0</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
         <v>3</v>
       </c>
       <c r="G28" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H28" s="15">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I28" s="14">
         <v>10</v>
@@ -1453,7 +1453,7 @@
         <v>66.666666666666</v>
       </c>
       <c r="L28" s="15">
-        <v>25</v>
+        <v>11.111111111111</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1497,10 +1497,10 @@
         <v>0</v>
       </c>
       <c r="M29" s="15">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
       <c r="N29" s="15">
-        <v>-95.652173913043</v>
+        <v>-95.833333333333</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1538,10 +1538,10 @@
         <v>0</v>
       </c>
       <c r="M30" s="15">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
       <c r="N30" s="15">
-        <v>-95.454545454545</v>
+        <v>-95.652173913043</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-023pct.xlsx
+++ b/data/source/weekly/cs-en-us-023pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">9</t>
+      <t xml:space="preserve">10</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/23/2026</t>
+      <t xml:space="preserve">3/2/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/1/2026</t>
+      <t xml:space="preserve">3/8/2026</t>
     </r>
   </si>
   <si>
@@ -892,8 +892,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>1</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -926,7 +926,7 @@
         <v>0</v>
       </c>
       <c r="N15" s="15">
-        <v>-85.714285714285</v>
+        <v>-86.666666666666</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -937,37 +937,37 @@
         <v>2</v>
       </c>
       <c r="D16" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E16" s="15">
-        <v>-60</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F16" s="14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G16" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H16" s="15">
-        <v>-37.5</v>
+        <v>-52.941176470588</v>
       </c>
       <c r="I16" s="14">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J16" s="14">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="K16" s="15">
-        <v>-42.5</v>
+        <v>-45.652173913043</v>
       </c>
       <c r="L16" s="15">
-        <v>-32.352941176470</v>
+        <v>-32.432432432432</v>
       </c>
       <c r="M16" s="15">
-        <v>-41.025641025641</v>
+        <v>-40.476190476190</v>
       </c>
       <c r="N16" s="15">
-        <v>-80.341880341880</v>
+        <v>-82.014388489208</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D17" s="14">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E17" s="15">
-        <v>-64.285714285714</v>
+        <v>28.571428571428</v>
       </c>
       <c r="F17" s="14">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G17" s="14">
         <v>41</v>
       </c>
       <c r="H17" s="15">
-        <v>-48.780487804878</v>
+        <v>-41.463414634146</v>
       </c>
       <c r="I17" s="14">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="J17" s="14">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="K17" s="15">
-        <v>-40.540540540540</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L17" s="15">
-        <v>-24.137931034482</v>
+        <v>-19.402985074626</v>
       </c>
       <c r="M17" s="15">
-        <v>91.304347826087</v>
+        <v>92.857142857142</v>
       </c>
       <c r="N17" s="15">
-        <v>-49.425287356321</v>
+        <v>-43.157894736842</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
+      <c r="C18" s="14">
+        <v>2</v>
       </c>
       <c r="D18" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F18" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G18" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H18" s="15">
-        <v>-25</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I18" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J18" s="14">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K18" s="15">
-        <v>-18.75</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="L18" s="15">
-        <v>-48</v>
+        <v>-53.125</v>
       </c>
       <c r="M18" s="15">
-        <v>0</v>
+        <v>15.384615384615</v>
       </c>
       <c r="N18" s="15">
-        <v>-81.428571428571</v>
+        <v>-80.769230769230</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,54 +1057,54 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D19" s="14">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E19" s="15">
-        <v>14.285714285714</v>
+        <v>0</v>
       </c>
       <c r="F19" s="14">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G19" s="14">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="H19" s="15">
-        <v>12</v>
+        <v>3.225806451612</v>
       </c>
       <c r="I19" s="14">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="J19" s="14">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="K19" s="15">
-        <v>-7.936507936507</v>
+        <v>-6.756756756756</v>
       </c>
       <c r="L19" s="15">
-        <v>-7.936507936507</v>
+        <v>1.470588235294</v>
       </c>
       <c r="M19" s="15">
-        <v>81.25</v>
+        <v>72.5</v>
       </c>
       <c r="N19" s="15">
-        <v>-44.230769230769</v>
+        <v>-41.025641025641</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
+      <c r="C20" s="14">
+        <v>1</v>
       </c>
       <c r="D20" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E20" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F20" s="14">
         <v>3</v>
@@ -1116,22 +1116,22 @@
         <v>-40</v>
       </c>
       <c r="I20" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J20" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K20" s="15">
         <v>0</v>
       </c>
       <c r="L20" s="15">
-        <v>-22.222222222222</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="M20" s="15">
-        <v>250</v>
+        <v>166.666666666667</v>
       </c>
       <c r="N20" s="15">
-        <v>-88.135593220339</v>
+        <v>-88.059701492537</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="D21" s="17">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E21" s="18">
-        <v>-44.827586206896</v>
+        <v>-7.407407407407</v>
       </c>
       <c r="F21" s="17">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="G21" s="17">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="H21" s="18">
-        <v>-26.373626373626</v>
+        <v>-27</v>
       </c>
       <c r="I21" s="17">
-        <v>147</v>
+        <v>173</v>
       </c>
       <c r="J21" s="17">
-        <v>203</v>
+        <v>230</v>
       </c>
       <c r="K21" s="18">
-        <v>-27.586206896551</v>
+        <v>-24.782608695652</v>
       </c>
       <c r="L21" s="18">
-        <v>-23.036649214659</v>
+        <v>-19.534883720930</v>
       </c>
       <c r="M21" s="18">
-        <v>31.25</v>
+        <v>34.108527131782</v>
       </c>
       <c r="N21" s="18">
-        <v>-67.763157894736</v>
+        <v>-66.537717601547</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D23" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E23" s="15">
-        <v>-62.5</v>
+        <v>0</v>
       </c>
       <c r="F23" s="14">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G23" s="14">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H23" s="15">
-        <v>-36.666666666666</v>
+        <v>-41.935483870967</v>
       </c>
       <c r="I23" s="14">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="J23" s="14">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="K23" s="15">
-        <v>-19.672131147541</v>
+        <v>-16.417910447761</v>
       </c>
       <c r="L23" s="15">
-        <v>-16.949152542372</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="M23" s="15">
-        <v>63.333333333333</v>
+        <v>64.705882352941</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="D24" s="14">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E24" s="15">
-        <v>-36.363636363636</v>
+        <v>41.176470588235</v>
       </c>
       <c r="F24" s="14">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="G24" s="14">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="H24" s="15">
-        <v>-29.166666666666</v>
+        <v>-5.882352941176</v>
       </c>
       <c r="I24" s="14">
-        <v>143</v>
+        <v>167</v>
       </c>
       <c r="J24" s="14">
-        <v>169</v>
+        <v>186</v>
       </c>
       <c r="K24" s="15">
-        <v>-15.384615384615</v>
+        <v>-10.215053763440</v>
       </c>
       <c r="L24" s="15">
-        <v>20.168067226890</v>
+        <v>21.014492753623</v>
       </c>
       <c r="M24" s="15">
-        <v>45.918367346938</v>
+        <v>51.818181818181</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D25" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E25" s="15">
-        <v>-33.333333333333</v>
+        <v>-12.5</v>
       </c>
       <c r="F25" s="14">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G25" s="14">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="H25" s="15">
-        <v>-29.411764705882</v>
+        <v>-43.243243243243</v>
       </c>
       <c r="I25" s="14">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="J25" s="14">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="K25" s="15">
-        <v>1.785714285714</v>
+        <v>0</v>
       </c>
       <c r="L25" s="15">
-        <v>200</v>
+        <v>166.666666666667</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D26" s="14">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="E26" s="15">
-        <v>-38.461538461538</v>
+        <v>366.666666666667</v>
       </c>
       <c r="F26" s="14">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G26" s="14">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H26" s="15">
-        <v>10.256410256410</v>
+        <v>10.810810810810</v>
       </c>
       <c r="I26" s="14">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="J26" s="14">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="K26" s="15">
-        <v>10</v>
+        <v>21.686746987951</v>
       </c>
       <c r="L26" s="15">
-        <v>-10.204081632653</v>
+        <v>-13.675213675213</v>
       </c>
       <c r="M26" s="15">
-        <v>-2.222222222222</v>
+        <v>-3.809523809523</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>1</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="C28" s="14">
+        <v>1</v>
+      </c>
+      <c r="D28" s="14">
+        <v>2</v>
+      </c>
+      <c r="E28" s="15">
+        <v>-50</v>
       </c>
       <c r="F28" s="14">
         <v>3</v>
       </c>
       <c r="G28" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H28" s="15">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="I28" s="14">
+        <v>11</v>
+      </c>
+      <c r="J28" s="14">
+        <v>8</v>
+      </c>
+      <c r="K28" s="15">
+        <v>37.5</v>
+      </c>
+      <c r="L28" s="15">
         <v>10</v>
-      </c>
-      <c r="J28" s="14">
-        <v>6</v>
-      </c>
-      <c r="K28" s="15">
-        <v>66.666666666666</v>
-      </c>
-      <c r="L28" s="15">
-        <v>11.111111111111</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,38 +1469,38 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
+      <c r="D29" s="14">
+        <v>1</v>
+      </c>
+      <c r="E29" s="15">
+        <v>-100</v>
       </c>
       <c r="F29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H29" s="13" t="s">
-        <v>21</v>
+      <c r="G29" s="14">
+        <v>1</v>
+      </c>
+      <c r="H29" s="15">
+        <v>-100</v>
       </c>
       <c r="I29" s="14">
         <v>1</v>
       </c>
-      <c r="J29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K29" s="13" t="s">
-        <v>21</v>
+      <c r="J29" s="14">
+        <v>1</v>
+      </c>
+      <c r="K29" s="15">
+        <v>0</v>
       </c>
       <c r="L29" s="15">
         <v>0</v>
       </c>
       <c r="M29" s="15">
-        <v>-75</v>
+        <v>-80</v>
       </c>
       <c r="N29" s="15">
-        <v>-95.833333333333</v>
+        <v>-96.153846153846</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1510,46 +1510,46 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
+      <c r="D30" s="14">
+        <v>1</v>
+      </c>
+      <c r="E30" s="15">
+        <v>-100</v>
       </c>
       <c r="F30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H30" s="13" t="s">
-        <v>21</v>
+      <c r="G30" s="14">
+        <v>1</v>
+      </c>
+      <c r="H30" s="15">
+        <v>-100</v>
       </c>
       <c r="I30" s="14">
         <v>1</v>
       </c>
-      <c r="J30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K30" s="13" t="s">
-        <v>21</v>
+      <c r="J30" s="14">
+        <v>1</v>
+      </c>
+      <c r="K30" s="15">
+        <v>0</v>
       </c>
       <c r="L30" s="15">
         <v>0</v>
       </c>
       <c r="M30" s="15">
-        <v>-75</v>
+        <v>-80</v>
       </c>
       <c r="N30" s="15">
-        <v>-95.652173913043</v>
+        <v>-96</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>20</v>
+      <c r="C31" s="14">
+        <v>1</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>
@@ -1557,8 +1557,8 @@
       <c r="E31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="13" t="s">
-        <v>20</v>
+      <c r="F31" s="14">
+        <v>1</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>
@@ -1566,8 +1566,8 @@
       <c r="H31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I31" s="13" t="s">
-        <v>20</v>
+      <c r="I31" s="14">
+        <v>1</v>
       </c>
       <c r="J31" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-023pct.xlsx
+++ b/data/source/weekly/cs-en-us-023pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">10</t>
+      <t xml:space="preserve">11</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/2/2026</t>
+      <t xml:space="preserve">3/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/8/2026</t>
+      <t xml:space="preserve">3/15/2026</t>
     </r>
   </si>
   <si>
@@ -902,7 +902,7 @@
         <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>20</v>
@@ -920,13 +920,13 @@
         <v>0</v>
       </c>
       <c r="L15" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M15" s="15">
         <v>0</v>
       </c>
       <c r="N15" s="15">
-        <v>-86.666666666666</v>
+        <v>-88.235294117647</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -937,37 +937,37 @@
         <v>2</v>
       </c>
       <c r="D16" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E16" s="15">
-        <v>-66.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="F16" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G16" s="14">
         <v>17</v>
       </c>
       <c r="H16" s="15">
-        <v>-52.941176470588</v>
+        <v>-47.058823529411</v>
       </c>
       <c r="I16" s="14">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J16" s="14">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="K16" s="15">
-        <v>-45.652173913043</v>
+        <v>-46</v>
       </c>
       <c r="L16" s="15">
-        <v>-32.432432432432</v>
+        <v>-30.769230769230</v>
       </c>
       <c r="M16" s="15">
-        <v>-40.476190476190</v>
+        <v>-46</v>
       </c>
       <c r="N16" s="15">
-        <v>-82.014388489208</v>
+        <v>-82.580645161290</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,37 +978,37 @@
         <v>9</v>
       </c>
       <c r="D17" s="14">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E17" s="15">
-        <v>28.571428571428</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="F17" s="14">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G17" s="14">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H17" s="15">
-        <v>-41.463414634146</v>
+        <v>-30.952380952381</v>
       </c>
       <c r="I17" s="14">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="J17" s="14">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K17" s="15">
-        <v>-33.333333333333</v>
+        <v>-30.434782608695</v>
       </c>
       <c r="L17" s="15">
-        <v>-19.402985074626</v>
+        <v>-17.948717948717</v>
       </c>
       <c r="M17" s="15">
-        <v>92.857142857142</v>
+        <v>113.333333333333</v>
       </c>
       <c r="N17" s="15">
-        <v>-43.157894736842</v>
+        <v>-40.186915887850</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,37 +1019,37 @@
         <v>2</v>
       </c>
       <c r="D18" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E18" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F18" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G18" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H18" s="15">
-        <v>-33.333333333333</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="I18" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J18" s="14">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K18" s="15">
-        <v>-16.666666666666</v>
+        <v>-19.047619047619</v>
       </c>
       <c r="L18" s="15">
-        <v>-53.125</v>
+        <v>-55.263157894736</v>
       </c>
       <c r="M18" s="15">
-        <v>15.384615384615</v>
+        <v>21.428571428571</v>
       </c>
       <c r="N18" s="15">
-        <v>-80.769230769230</v>
+        <v>-79.761904761904</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,81 +1057,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D19" s="14">
         <v>11</v>
       </c>
       <c r="E19" s="15">
-        <v>0</v>
+        <v>9.090909090909</v>
       </c>
       <c r="F19" s="14">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G19" s="14">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H19" s="15">
-        <v>3.225806451612</v>
+        <v>3.030303030303</v>
       </c>
       <c r="I19" s="14">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="J19" s="14">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="K19" s="15">
-        <v>-6.756756756756</v>
+        <v>-5.882352941176</v>
       </c>
       <c r="L19" s="15">
-        <v>1.470588235294</v>
+        <v>5.263157894736</v>
       </c>
       <c r="M19" s="15">
-        <v>72.5</v>
+        <v>77.777777777777</v>
       </c>
       <c r="N19" s="15">
-        <v>-41.025641025641</v>
+        <v>-37.5</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="14">
-        <v>1</v>
+      <c r="C20" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D20" s="14">
         <v>1</v>
       </c>
       <c r="E20" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F20" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G20" s="14">
         <v>5</v>
       </c>
       <c r="H20" s="15">
-        <v>-40</v>
+        <v>-80</v>
       </c>
       <c r="I20" s="14">
         <v>8</v>
       </c>
       <c r="J20" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K20" s="15">
-        <v>0</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="L20" s="15">
-        <v>-11.111111111111</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="M20" s="15">
-        <v>166.666666666667</v>
+        <v>100</v>
       </c>
       <c r="N20" s="15">
-        <v>-88.059701492537</v>
+        <v>-89.473684210526</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,37 +1142,37 @@
         <v>25</v>
       </c>
       <c r="D21" s="17">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E21" s="18">
-        <v>-7.407407407407</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="F21" s="17">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G21" s="17">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="H21" s="18">
-        <v>-27</v>
+        <v>-24.038461538461</v>
       </c>
       <c r="I21" s="17">
-        <v>173</v>
+        <v>198</v>
       </c>
       <c r="J21" s="17">
-        <v>230</v>
+        <v>260</v>
       </c>
       <c r="K21" s="18">
-        <v>-24.782608695652</v>
+        <v>-23.846153846153</v>
       </c>
       <c r="L21" s="18">
-        <v>-19.534883720930</v>
+        <v>-19.183673469387</v>
       </c>
       <c r="M21" s="18">
-        <v>34.108527131782</v>
+        <v>35.616438356164</v>
       </c>
       <c r="N21" s="18">
-        <v>-66.537717601547</v>
+        <v>-65.445026178010</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1224,34 +1224,34 @@
         <v>6</v>
       </c>
       <c r="D23" s="14">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E23" s="15">
-        <v>0</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="F23" s="14">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G23" s="14">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H23" s="15">
-        <v>-41.935483870967</v>
+        <v>-37.5</v>
       </c>
       <c r="I23" s="14">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="J23" s="14">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="K23" s="15">
-        <v>-16.417910447761</v>
+        <v>-19.230769230769</v>
       </c>
       <c r="L23" s="15">
-        <v>-11.111111111111</v>
+        <v>-10</v>
       </c>
       <c r="M23" s="15">
-        <v>64.705882352941</v>
+        <v>61.538461538461</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1265,34 +1265,34 @@
         <v>24</v>
       </c>
       <c r="D24" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E24" s="15">
-        <v>41.176470588235</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F24" s="14">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="G24" s="14">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="H24" s="15">
-        <v>-5.882352941176</v>
+        <v>1.219512195121</v>
       </c>
       <c r="I24" s="14">
-        <v>167</v>
+        <v>191</v>
       </c>
       <c r="J24" s="14">
-        <v>186</v>
+        <v>204</v>
       </c>
       <c r="K24" s="15">
-        <v>-10.215053763440</v>
+        <v>-6.372549019607</v>
       </c>
       <c r="L24" s="15">
-        <v>21.014492753623</v>
+        <v>24.025974025974</v>
       </c>
       <c r="M24" s="15">
-        <v>51.818181818181</v>
+        <v>63.247863247863</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D25" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E25" s="15">
-        <v>-12.5</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F25" s="14">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G25" s="14">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="H25" s="15">
-        <v>-43.243243243243</v>
+        <v>-35.483870967741</v>
       </c>
       <c r="I25" s="14">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="J25" s="14">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="K25" s="15">
-        <v>0</v>
+        <v>-2.857142857142</v>
       </c>
       <c r="L25" s="15">
-        <v>166.666666666667</v>
+        <v>151.851851851852</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D26" s="14">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="E26" s="15">
-        <v>366.666666666667</v>
+        <v>-5.882352941176</v>
       </c>
       <c r="F26" s="14">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="G26" s="14">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="H26" s="15">
-        <v>10.810810810810</v>
+        <v>8.888888888888</v>
       </c>
       <c r="I26" s="14">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="J26" s="14">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="K26" s="15">
-        <v>21.686746987951</v>
+        <v>17</v>
       </c>
       <c r="L26" s="15">
-        <v>-13.675213675213</v>
+        <v>-7.874015748031</v>
       </c>
       <c r="M26" s="15">
-        <v>-3.809523809523</v>
+        <v>-0.847457627118</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,32 +1387,32 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="D27" s="14">
+        <v>1</v>
+      </c>
+      <c r="E27" s="15">
+        <v>-100</v>
       </c>
       <c r="F27" s="14">
-        <v>2</v>
-      </c>
-      <c r="G27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H27" s="13" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="G27" s="14">
+        <v>1</v>
+      </c>
+      <c r="H27" s="15">
+        <v>0</v>
       </c>
       <c r="I27" s="14">
         <v>2</v>
       </c>
       <c r="J27" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K27" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L27" s="15">
-        <v>-33.333333333333</v>
+        <v>-60</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
+      <c r="C28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="14">
         <v>1</v>
       </c>
-      <c r="D28" s="14">
+      <c r="E28" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F28" s="14">
         <v>2</v>
       </c>
-      <c r="E28" s="15">
+      <c r="G28" s="14">
+        <v>4</v>
+      </c>
+      <c r="H28" s="15">
         <v>-50</v>
-      </c>
-      <c r="F28" s="14">
-        <v>3</v>
-      </c>
-      <c r="G28" s="14">
-        <v>3</v>
-      </c>
-      <c r="H28" s="15">
-        <v>0</v>
       </c>
       <c r="I28" s="14">
         <v>11</v>
       </c>
       <c r="J28" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K28" s="15">
-        <v>37.5</v>
+        <v>22.222222222222</v>
       </c>
       <c r="L28" s="15">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,11 +1469,11 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="14">
-        <v>1</v>
-      </c>
-      <c r="E29" s="15">
-        <v>-100</v>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F29" s="13" t="s">
         <v>20</v>
@@ -1510,11 +1510,11 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="14">
-        <v>1</v>
-      </c>
-      <c r="E30" s="15">
-        <v>-100</v>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F30" s="13" t="s">
         <v>20</v>
@@ -1548,8 +1548,8 @@
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="14">
-        <v>1</v>
+      <c r="C31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>
@@ -1557,8 +1557,8 @@
       <c r="E31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="14">
-        <v>1</v>
+      <c r="F31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>
@@ -1566,8 +1566,8 @@
       <c r="H31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I31" s="14">
-        <v>1</v>
+      <c r="I31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="J31" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-023pct.xlsx
+++ b/data/source/weekly/cs-en-us-023pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">11</t>
+      <t xml:space="preserve">12</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/9/2026</t>
+      <t xml:space="preserve">3/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/15/2026</t>
+      <t xml:space="preserve">3/22/2026</t>
     </r>
   </si>
   <si>
@@ -892,41 +892,41 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="C15" s="14">
+        <v>2</v>
+      </c>
+      <c r="D15" s="14">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15">
+        <v>100</v>
       </c>
       <c r="F15" s="14">
+        <v>3</v>
+      </c>
+      <c r="G15" s="14">
         <v>1</v>
       </c>
-      <c r="G15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H15" s="13" t="s">
-        <v>21</v>
+      <c r="H15" s="15">
+        <v>200</v>
       </c>
       <c r="I15" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J15" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K15" s="15">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L15" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M15" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N15" s="15">
-        <v>-88.235294117647</v>
+        <v>-76.470588235294</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -937,37 +937,37 @@
         <v>2</v>
       </c>
       <c r="D16" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E16" s="15">
+        <v>-66.666666666666</v>
+      </c>
+      <c r="F16" s="14">
+        <v>7</v>
+      </c>
+      <c r="G16" s="14">
+        <v>21</v>
+      </c>
+      <c r="H16" s="15">
+        <v>-66.666666666666</v>
+      </c>
+      <c r="I16" s="14">
+        <v>28</v>
+      </c>
+      <c r="J16" s="14">
+        <v>56</v>
+      </c>
+      <c r="K16" s="15">
         <v>-50</v>
       </c>
-      <c r="F16" s="14">
-        <v>9</v>
-      </c>
-      <c r="G16" s="14">
-        <v>17</v>
-      </c>
-      <c r="H16" s="15">
-        <v>-47.058823529411</v>
-      </c>
-      <c r="I16" s="14">
-        <v>27</v>
-      </c>
-      <c r="J16" s="14">
-        <v>50</v>
-      </c>
-      <c r="K16" s="15">
-        <v>-46</v>
-      </c>
       <c r="L16" s="15">
-        <v>-30.769230769230</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M16" s="15">
-        <v>-46</v>
+        <v>-49.090909090909</v>
       </c>
       <c r="N16" s="15">
-        <v>-82.580645161290</v>
+        <v>-83.625730994152</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D17" s="14">
         <v>11</v>
       </c>
       <c r="E17" s="15">
-        <v>-18.181818181818</v>
+        <v>-72.727272727272</v>
       </c>
       <c r="F17" s="14">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G17" s="14">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H17" s="15">
-        <v>-30.952380952381</v>
+        <v>-37.209302325581</v>
       </c>
       <c r="I17" s="14">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="J17" s="14">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="K17" s="15">
-        <v>-30.434782608695</v>
+        <v>-33.980582524271</v>
       </c>
       <c r="L17" s="15">
-        <v>-17.948717948717</v>
+        <v>-20</v>
       </c>
       <c r="M17" s="15">
-        <v>113.333333333333</v>
+        <v>83.783783783783</v>
       </c>
       <c r="N17" s="15">
-        <v>-40.186915887850</v>
+        <v>-40.869565217391</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="14">
-        <v>2</v>
+      <c r="C18" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D18" s="14">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E18" s="15">
-        <v>-33.333333333333</v>
+        <v>-100</v>
       </c>
       <c r="F18" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G18" s="14">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="H18" s="15">
-        <v>-28.571428571428</v>
+        <v>-69.230769230769</v>
       </c>
       <c r="I18" s="14">
         <v>17</v>
       </c>
       <c r="J18" s="14">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="K18" s="15">
-        <v>-19.047619047619</v>
+        <v>-39.285714285714</v>
       </c>
       <c r="L18" s="15">
-        <v>-55.263157894736</v>
+        <v>-59.523809523809</v>
       </c>
       <c r="M18" s="15">
-        <v>21.428571428571</v>
+        <v>13.333333333333</v>
       </c>
       <c r="N18" s="15">
-        <v>-79.761904761904</v>
+        <v>-81.720430107526</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,81 +1057,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D19" s="14">
         <v>11</v>
       </c>
       <c r="E19" s="15">
-        <v>9.090909090909</v>
+        <v>27.272727272727</v>
       </c>
       <c r="F19" s="14">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="G19" s="14">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="H19" s="15">
-        <v>3.030303030303</v>
+        <v>10</v>
       </c>
       <c r="I19" s="14">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="J19" s="14">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K19" s="15">
-        <v>-5.882352941176</v>
+        <v>-2.083333333333</v>
       </c>
       <c r="L19" s="15">
-        <v>5.263157894736</v>
+        <v>11.904761904761</v>
       </c>
       <c r="M19" s="15">
-        <v>77.777777777777</v>
+        <v>84.313725490196</v>
       </c>
       <c r="N19" s="15">
-        <v>-37.5</v>
+        <v>-33.802816901408</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
+      <c r="C20" s="14">
+        <v>1</v>
       </c>
       <c r="D20" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E20" s="15">
-        <v>-100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F20" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G20" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H20" s="15">
-        <v>-80</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="I20" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J20" s="14">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K20" s="15">
-        <v>-11.111111111111</v>
+        <v>-25</v>
       </c>
       <c r="L20" s="15">
-        <v>-27.272727272727</v>
+        <v>-43.75</v>
       </c>
       <c r="M20" s="15">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="N20" s="15">
-        <v>-89.473684210526</v>
+        <v>-89.285714285714</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D21" s="17">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="E21" s="18">
-        <v>-16.666666666666</v>
+        <v>-43.589743589743</v>
       </c>
       <c r="F21" s="17">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="G21" s="17">
-        <v>104</v>
+        <v>125</v>
       </c>
       <c r="H21" s="18">
-        <v>-24.038461538461</v>
+        <v>-30.4</v>
       </c>
       <c r="I21" s="17">
-        <v>198</v>
+        <v>220</v>
       </c>
       <c r="J21" s="17">
-        <v>260</v>
+        <v>299</v>
       </c>
       <c r="K21" s="18">
-        <v>-23.846153846153</v>
+        <v>-26.421404682274</v>
       </c>
       <c r="L21" s="18">
-        <v>-19.183673469387</v>
+        <v>-19.117647058823</v>
       </c>
       <c r="M21" s="18">
-        <v>35.616438356164</v>
+        <v>33.333333333333</v>
       </c>
       <c r="N21" s="18">
-        <v>-65.445026178010</v>
+        <v>-64.968152866242</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D23" s="14">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E23" s="15">
-        <v>-45.454545454545</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="F23" s="14">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G23" s="14">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="H23" s="15">
-        <v>-37.5</v>
+        <v>-35.897435897435</v>
       </c>
       <c r="I23" s="14">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="J23" s="14">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="K23" s="15">
-        <v>-19.230769230769</v>
+        <v>-20.652173913043</v>
       </c>
       <c r="L23" s="15">
-        <v>-10</v>
+        <v>-5.194805194805</v>
       </c>
       <c r="M23" s="15">
-        <v>61.538461538461</v>
+        <v>65.909090909090</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
+        <v>22</v>
+      </c>
+      <c r="D24" s="14">
         <v>24</v>
       </c>
-      <c r="D24" s="14">
-        <v>18</v>
-      </c>
       <c r="E24" s="15">
-        <v>33.333333333333</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="F24" s="14">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G24" s="14">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H24" s="15">
-        <v>1.219512195121</v>
+        <v>3.703703703703</v>
       </c>
       <c r="I24" s="14">
-        <v>191</v>
+        <v>213</v>
       </c>
       <c r="J24" s="14">
-        <v>204</v>
+        <v>228</v>
       </c>
       <c r="K24" s="15">
-        <v>-6.372549019607</v>
+        <v>-6.578947368421</v>
       </c>
       <c r="L24" s="15">
-        <v>24.025974025974</v>
+        <v>24.561403508771</v>
       </c>
       <c r="M24" s="15">
-        <v>63.247863247863</v>
+        <v>71.774193548387</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D25" s="14">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E25" s="15">
-        <v>-33.333333333333</v>
+        <v>-70</v>
       </c>
       <c r="F25" s="14">
         <v>20</v>
       </c>
       <c r="G25" s="14">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H25" s="15">
-        <v>-35.483870967741</v>
+        <v>-39.393939393939</v>
       </c>
       <c r="I25" s="14">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="J25" s="14">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="K25" s="15">
-        <v>-2.857142857142</v>
+        <v>-11.25</v>
       </c>
       <c r="L25" s="15">
-        <v>151.851851851852</v>
+        <v>136.666666666667</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D26" s="14">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E26" s="15">
-        <v>-5.882352941176</v>
+        <v>-50</v>
       </c>
       <c r="F26" s="14">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G26" s="14">
         <v>45</v>
       </c>
       <c r="H26" s="15">
-        <v>8.888888888888</v>
+        <v>6.666666666666</v>
       </c>
       <c r="I26" s="14">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="J26" s="14">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="K26" s="15">
-        <v>17</v>
+        <v>13.392857142857</v>
       </c>
       <c r="L26" s="15">
-        <v>-7.874015748031</v>
+        <v>-12.413793103448</v>
       </c>
       <c r="M26" s="15">
-        <v>-0.847457627118</v>
+        <v>-13.013698630137</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="14">
+        <v>2</v>
       </c>
       <c r="D27" s="14">
         <v>1</v>
       </c>
       <c r="E27" s="15">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="F27" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G27" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H27" s="15">
+        <v>50</v>
+      </c>
+      <c r="I27" s="14">
+        <v>4</v>
+      </c>
+      <c r="J27" s="14">
+        <v>4</v>
+      </c>
+      <c r="K27" s="15">
         <v>0</v>
       </c>
-      <c r="I27" s="14">
-        <v>2</v>
-      </c>
-      <c r="J27" s="14">
-        <v>3</v>
-      </c>
-      <c r="K27" s="15">
-        <v>-33.333333333333</v>
-      </c>
       <c r="L27" s="15">
-        <v>-60</v>
+        <v>-20</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,14 +1425,14 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="14">
+        <v>1</v>
       </c>
       <c r="D28" s="14">
         <v>1</v>
       </c>
       <c r="E28" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F28" s="14">
         <v>2</v>
@@ -1444,16 +1444,16 @@
         <v>-50</v>
       </c>
       <c r="I28" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J28" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K28" s="15">
-        <v>22.222222222222</v>
+        <v>20</v>
       </c>
       <c r="L28" s="15">
-        <v>0</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,17 +1469,17 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
+      <c r="D29" s="14">
+        <v>2</v>
+      </c>
+      <c r="E29" s="15">
+        <v>-100</v>
       </c>
       <c r="F29" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G29" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H29" s="15">
         <v>-100</v>
@@ -1488,16 +1488,16 @@
         <v>1</v>
       </c>
       <c r="J29" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K29" s="15">
-        <v>0</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="L29" s="15">
         <v>0</v>
       </c>
       <c r="M29" s="15">
-        <v>-80</v>
+        <v>-87.5</v>
       </c>
       <c r="N29" s="15">
         <v>-96.153846153846</v>
@@ -1510,17 +1510,17 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
+      <c r="D30" s="14">
+        <v>2</v>
+      </c>
+      <c r="E30" s="15">
+        <v>-100</v>
       </c>
       <c r="F30" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G30" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H30" s="15">
         <v>-100</v>
@@ -1529,16 +1529,16 @@
         <v>1</v>
       </c>
       <c r="J30" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K30" s="15">
-        <v>0</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="L30" s="15">
         <v>0</v>
       </c>
       <c r="M30" s="15">
-        <v>-80</v>
+        <v>-87.5</v>
       </c>
       <c r="N30" s="15">
         <v>-96</v>

--- a/data/source/weekly/cs-en-us-023pct.xlsx
+++ b/data/source/weekly/cs-en-us-023pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">12</t>
+      <t xml:space="preserve">13</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/16/2026</t>
+      <t xml:space="preserve">3/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/22/2026</t>
+      <t xml:space="preserve">3/29/2026</t>
     </r>
   </si>
   <si>
@@ -892,23 +892,23 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="14">
         <v>2</v>
-      </c>
-      <c r="D15" s="14">
-        <v>1</v>
-      </c>
-      <c r="E15" s="15">
-        <v>100</v>
-      </c>
-      <c r="F15" s="14">
-        <v>3</v>
       </c>
       <c r="G15" s="14">
         <v>1</v>
       </c>
       <c r="H15" s="15">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I15" s="14">
         <v>4</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D16" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E16" s="15">
-        <v>-66.666666666666</v>
+        <v>25</v>
       </c>
       <c r="F16" s="14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G16" s="14">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H16" s="15">
-        <v>-66.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="I16" s="14">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="J16" s="14">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="K16" s="15">
-        <v>-50</v>
+        <v>-45</v>
       </c>
       <c r="L16" s="15">
-        <v>-33.333333333333</v>
+        <v>-29.787234042553</v>
       </c>
       <c r="M16" s="15">
-        <v>-49.090909090909</v>
+        <v>-45.901639344262</v>
       </c>
       <c r="N16" s="15">
-        <v>-83.625730994152</v>
+        <v>-81.967213114754</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D17" s="14">
         <v>11</v>
       </c>
       <c r="E17" s="15">
-        <v>-72.727272727272</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="F17" s="14">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G17" s="14">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="H17" s="15">
-        <v>-37.209302325581</v>
+        <v>-30</v>
       </c>
       <c r="I17" s="14">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="J17" s="14">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="K17" s="15">
-        <v>-33.980582524271</v>
+        <v>-35.087719298245</v>
       </c>
       <c r="L17" s="15">
-        <v>-20</v>
+        <v>-23.711340206185</v>
       </c>
       <c r="M17" s="15">
-        <v>83.783783783783</v>
+        <v>89.743589743589</v>
       </c>
       <c r="N17" s="15">
-        <v>-40.869565217391</v>
+        <v>-45.185185185185</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
+      <c r="C18" s="14">
+        <v>1</v>
       </c>
       <c r="D18" s="14">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E18" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="F18" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G18" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H18" s="15">
-        <v>-69.230769230769</v>
+        <v>-64.285714285714</v>
       </c>
       <c r="I18" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J18" s="14">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K18" s="15">
-        <v>-39.285714285714</v>
+        <v>-40</v>
       </c>
       <c r="L18" s="15">
-        <v>-59.523809523809</v>
+        <v>-61.702127659574</v>
       </c>
       <c r="M18" s="15">
-        <v>13.333333333333</v>
+        <v>12.5</v>
       </c>
       <c r="N18" s="15">
-        <v>-81.720430107526</v>
+        <v>-82</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D19" s="14">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E19" s="15">
-        <v>27.272727272727</v>
+        <v>20</v>
       </c>
       <c r="F19" s="14">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G19" s="14">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="H19" s="15">
-        <v>10</v>
+        <v>13.157894736842</v>
       </c>
       <c r="I19" s="14">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="J19" s="14">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="K19" s="15">
-        <v>-2.083333333333</v>
+        <v>-0.990099009900</v>
       </c>
       <c r="L19" s="15">
-        <v>11.904761904761</v>
+        <v>12.359550561797</v>
       </c>
       <c r="M19" s="15">
-        <v>84.313725490196</v>
+        <v>72.413793103448</v>
       </c>
       <c r="N19" s="15">
-        <v>-33.802816901408</v>
+        <v>-36.305732484076</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1107,31 +1107,31 @@
         <v>-66.666666666666</v>
       </c>
       <c r="F20" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G20" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H20" s="15">
-        <v>-71.428571428571</v>
+        <v>-62.5</v>
       </c>
       <c r="I20" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J20" s="14">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K20" s="15">
-        <v>-25</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L20" s="15">
-        <v>-43.75</v>
+        <v>-41.176470588235</v>
       </c>
       <c r="M20" s="15">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="N20" s="15">
-        <v>-89.285714285714</v>
+        <v>-88.764044943820</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D21" s="17">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="E21" s="18">
-        <v>-43.589743589743</v>
+        <v>-24</v>
       </c>
       <c r="F21" s="17">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="G21" s="17">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="H21" s="18">
-        <v>-30.4</v>
+        <v>-24.793388429752</v>
       </c>
       <c r="I21" s="17">
-        <v>220</v>
+        <v>239</v>
       </c>
       <c r="J21" s="17">
-        <v>299</v>
+        <v>324</v>
       </c>
       <c r="K21" s="18">
-        <v>-26.421404682274</v>
+        <v>-26.234567901234</v>
       </c>
       <c r="L21" s="18">
-        <v>-19.117647058823</v>
+        <v>-20.333333333333</v>
       </c>
       <c r="M21" s="18">
-        <v>33.333333333333</v>
+        <v>31.318681318681</v>
       </c>
       <c r="N21" s="18">
-        <v>-64.968152866242</v>
+        <v>-65.211062590975</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D23" s="14">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E23" s="15">
-        <v>-42.857142857142</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="F23" s="14">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G23" s="14">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="H23" s="15">
-        <v>-35.897435897435</v>
+        <v>-32.558139534883</v>
       </c>
       <c r="I23" s="14">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="J23" s="14">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="K23" s="15">
-        <v>-20.652173913043</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="L23" s="15">
-        <v>-5.194805194805</v>
+        <v>-5.882352941176</v>
       </c>
       <c r="M23" s="15">
-        <v>65.909090909090</v>
+        <v>63.265306122449</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D24" s="14">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E24" s="15">
-        <v>-8.333333333333</v>
+        <v>-32</v>
       </c>
       <c r="F24" s="14">
+        <v>86</v>
+      </c>
+      <c r="G24" s="14">
         <v>84</v>
       </c>
-      <c r="G24" s="14">
-        <v>81</v>
-      </c>
       <c r="H24" s="15">
-        <v>3.703703703703</v>
+        <v>2.380952380952</v>
       </c>
       <c r="I24" s="14">
-        <v>213</v>
+        <v>230</v>
       </c>
       <c r="J24" s="14">
-        <v>228</v>
+        <v>253</v>
       </c>
       <c r="K24" s="15">
-        <v>-6.578947368421</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="L24" s="15">
-        <v>24.561403508771</v>
+        <v>22.340425531914</v>
       </c>
       <c r="M24" s="15">
-        <v>71.774193548387</v>
+        <v>71.641791044776</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D25" s="14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E25" s="15">
-        <v>-70</v>
+        <v>-75</v>
       </c>
       <c r="F25" s="14">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G25" s="14">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H25" s="15">
-        <v>-39.393939393939</v>
+        <v>-50</v>
       </c>
       <c r="I25" s="14">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J25" s="14">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="K25" s="15">
-        <v>-11.25</v>
+        <v>-17.045454545454</v>
       </c>
       <c r="L25" s="15">
-        <v>136.666666666667</v>
+        <v>128.125</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D26" s="14">
         <v>12</v>
       </c>
       <c r="E26" s="15">
-        <v>-50</v>
+        <v>16.666666666666</v>
       </c>
       <c r="F26" s="14">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="G26" s="14">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H26" s="15">
-        <v>6.666666666666</v>
+        <v>18.181818181818</v>
       </c>
       <c r="I26" s="14">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="J26" s="14">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="K26" s="15">
-        <v>13.392857142857</v>
+        <v>12.903225806451</v>
       </c>
       <c r="L26" s="15">
-        <v>-12.413793103448</v>
+        <v>-11.392405063291</v>
       </c>
       <c r="M26" s="15">
-        <v>-13.013698630137</v>
+        <v>-13.580246913580</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,23 +1384,23 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="14">
         <v>2</v>
-      </c>
-      <c r="D27" s="14">
-        <v>1</v>
-      </c>
-      <c r="E27" s="15">
-        <v>100</v>
-      </c>
-      <c r="F27" s="14">
-        <v>3</v>
       </c>
       <c r="G27" s="14">
         <v>2</v>
       </c>
       <c r="H27" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I27" s="14">
         <v>4</v>
@@ -1428,32 +1428,32 @@
       <c r="C28" s="14">
         <v>1</v>
       </c>
-      <c r="D28" s="14">
-        <v>1</v>
-      </c>
-      <c r="E28" s="15">
-        <v>0</v>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G28" s="14">
         <v>4</v>
       </c>
       <c r="H28" s="15">
-        <v>-50</v>
+        <v>-25</v>
       </c>
       <c r="I28" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J28" s="14">
         <v>10</v>
       </c>
       <c r="K28" s="15">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="L28" s="15">
-        <v>-7.692307692307</v>
+        <v>0</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,11 +1469,11 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="14">
-        <v>2</v>
-      </c>
-      <c r="E29" s="15">
-        <v>-100</v>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F29" s="13" t="s">
         <v>20</v>
@@ -1500,7 +1500,7 @@
         <v>-87.5</v>
       </c>
       <c r="N29" s="15">
-        <v>-96.153846153846</v>
+        <v>-96.296296296296</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1510,11 +1510,11 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="14">
-        <v>2</v>
-      </c>
-      <c r="E30" s="15">
-        <v>-100</v>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F30" s="13" t="s">
         <v>20</v>
@@ -1541,7 +1541,7 @@
         <v>-87.5</v>
       </c>
       <c r="N30" s="15">
-        <v>-96</v>
+        <v>-96.153846153846</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-023pct.xlsx
+++ b/data/source/weekly/cs-en-us-023pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">13</t>
+      <t xml:space="preserve">14</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/23/2026</t>
+      <t xml:space="preserve">3/30/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/29/2026</t>
+      <t xml:space="preserve">4/5/2026</t>
     </r>
   </si>
   <si>
@@ -895,29 +895,29 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="D15" s="14">
+        <v>3</v>
+      </c>
+      <c r="E15" s="15">
+        <v>-100</v>
       </c>
       <c r="F15" s="14">
         <v>2</v>
       </c>
       <c r="G15" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H15" s="15">
-        <v>100</v>
+        <v>-50</v>
       </c>
       <c r="I15" s="14">
         <v>4</v>
       </c>
       <c r="J15" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K15" s="15">
-        <v>33.333333333333</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L15" s="15">
         <v>100</v>
@@ -926,7 +926,7 @@
         <v>100</v>
       </c>
       <c r="N15" s="15">
-        <v>-76.470588235294</v>
+        <v>-77.777777777777</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D16" s="14">
         <v>4</v>
       </c>
       <c r="E16" s="15">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F16" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G16" s="14">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H16" s="15">
-        <v>-50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I16" s="14">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J16" s="14">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="K16" s="15">
-        <v>-45</v>
+        <v>-42.1875</v>
       </c>
       <c r="L16" s="15">
-        <v>-29.787234042553</v>
+        <v>-26</v>
       </c>
       <c r="M16" s="15">
-        <v>-45.901639344262</v>
+        <v>-40.322580645161</v>
       </c>
       <c r="N16" s="15">
-        <v>-81.967213114754</v>
+        <v>-81.951219512195</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D17" s="14">
         <v>11</v>
       </c>
       <c r="E17" s="15">
-        <v>-45.454545454545</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="F17" s="14">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G17" s="14">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H17" s="15">
-        <v>-30</v>
+        <v>-40.909090909090</v>
       </c>
       <c r="I17" s="14">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="J17" s="14">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="K17" s="15">
-        <v>-35.087719298245</v>
+        <v>-35.2</v>
       </c>
       <c r="L17" s="15">
-        <v>-23.711340206185</v>
+        <v>-25.688073394495</v>
       </c>
       <c r="M17" s="15">
-        <v>89.743589743589</v>
+        <v>102.5</v>
       </c>
       <c r="N17" s="15">
-        <v>-45.185185185185</v>
+        <v>-45.270270270270</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="14">
+      <c r="C18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="14">
         <v>1</v>
       </c>
-      <c r="D18" s="14">
-        <v>2</v>
-      </c>
       <c r="E18" s="15">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="F18" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G18" s="14">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H18" s="15">
-        <v>-64.285714285714</v>
+        <v>-76.923076923076</v>
       </c>
       <c r="I18" s="14">
         <v>18</v>
       </c>
       <c r="J18" s="14">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K18" s="15">
-        <v>-40</v>
+        <v>-41.935483870967</v>
       </c>
       <c r="L18" s="15">
-        <v>-61.702127659574</v>
+        <v>-64</v>
       </c>
       <c r="M18" s="15">
-        <v>12.5</v>
+        <v>5.882352941176</v>
       </c>
       <c r="N18" s="15">
-        <v>-82</v>
+        <v>-83.333333333333</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,81 +1057,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D19" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E19" s="15">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="F19" s="14">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="G19" s="14">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="H19" s="15">
-        <v>13.157894736842</v>
+        <v>25.806451612903</v>
       </c>
       <c r="I19" s="14">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="J19" s="14">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="K19" s="15">
-        <v>-0.990099009900</v>
+        <v>2.857142857142</v>
       </c>
       <c r="L19" s="15">
-        <v>12.359550561797</v>
+        <v>10.204081632653</v>
       </c>
       <c r="M19" s="15">
-        <v>72.413793103448</v>
+        <v>80</v>
       </c>
       <c r="N19" s="15">
-        <v>-36.305732484076</v>
+        <v>-36.470588235294</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="14">
+      <c r="C20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="14">
         <v>1</v>
       </c>
-      <c r="D20" s="14">
-        <v>3</v>
-      </c>
       <c r="E20" s="15">
-        <v>-66.666666666666</v>
+        <v>-100</v>
       </c>
       <c r="F20" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G20" s="14">
         <v>8</v>
       </c>
       <c r="H20" s="15">
-        <v>-62.5</v>
+        <v>-75</v>
       </c>
       <c r="I20" s="14">
         <v>10</v>
       </c>
       <c r="J20" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K20" s="15">
-        <v>-33.333333333333</v>
+        <v>-37.5</v>
       </c>
       <c r="L20" s="15">
-        <v>-41.176470588235</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="M20" s="15">
         <v>100</v>
       </c>
       <c r="N20" s="15">
-        <v>-88.764044943820</v>
+        <v>-89.473684210526</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,48 +1139,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D21" s="17">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E21" s="18">
-        <v>-24</v>
+        <v>-25</v>
       </c>
       <c r="F21" s="17">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="G21" s="17">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="H21" s="18">
-        <v>-24.793388429752</v>
+        <v>-28.813559322033</v>
       </c>
       <c r="I21" s="17">
-        <v>239</v>
+        <v>258</v>
       </c>
       <c r="J21" s="17">
-        <v>324</v>
+        <v>348</v>
       </c>
       <c r="K21" s="18">
-        <v>-26.234567901234</v>
+        <v>-25.862068965517</v>
       </c>
       <c r="L21" s="18">
-        <v>-20.333333333333</v>
+        <v>-21.580547112462</v>
       </c>
       <c r="M21" s="18">
-        <v>31.318681318681</v>
+        <v>37.967914438502</v>
       </c>
       <c r="N21" s="18">
-        <v>-65.211062590975</v>
+        <v>-65.6</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="14">
+        <v>1</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1188,8 +1188,8 @@
       <c r="E22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F22" s="13" t="s">
-        <v>20</v>
+      <c r="F22" s="14">
+        <v>1</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>20</v>
@@ -1198,19 +1198,19 @@
         <v>21</v>
       </c>
       <c r="I22" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J22" s="14">
         <v>1</v>
       </c>
       <c r="K22" s="15">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="L22" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M22" s="15">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D23" s="14">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E23" s="15">
-        <v>-41.666666666666</v>
+        <v>-40</v>
       </c>
       <c r="F23" s="14">
         <v>29</v>
       </c>
       <c r="G23" s="14">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="H23" s="15">
-        <v>-32.558139534883</v>
+        <v>-38.297872340425</v>
       </c>
       <c r="I23" s="14">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="J23" s="14">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="K23" s="15">
-        <v>-23.076923076923</v>
+        <v>-24.561403508771</v>
       </c>
       <c r="L23" s="15">
-        <v>-5.882352941176</v>
+        <v>-10.416666666666</v>
       </c>
       <c r="M23" s="15">
-        <v>63.265306122449</v>
+        <v>72</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D24" s="14">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E24" s="15">
-        <v>-32</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="F24" s="14">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="G24" s="14">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H24" s="15">
-        <v>2.380952380952</v>
+        <v>-22.105263157894</v>
       </c>
       <c r="I24" s="14">
-        <v>230</v>
+        <v>242</v>
       </c>
       <c r="J24" s="14">
-        <v>253</v>
+        <v>281</v>
       </c>
       <c r="K24" s="15">
-        <v>-9.090909090909</v>
+        <v>-13.879003558718</v>
       </c>
       <c r="L24" s="15">
-        <v>22.340425531914</v>
+        <v>21.608040201005</v>
       </c>
       <c r="M24" s="15">
-        <v>71.641791044776</v>
+        <v>64.625850340136</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D25" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E25" s="15">
-        <v>-75</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F25" s="14">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G25" s="14">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H25" s="15">
-        <v>-50</v>
+        <v>-63.636363636363</v>
       </c>
       <c r="I25" s="14">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="J25" s="14">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="K25" s="15">
-        <v>-17.045454545454</v>
+        <v>-21.649484536082</v>
       </c>
       <c r="L25" s="15">
-        <v>128.125</v>
+        <v>111.111111111111</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D26" s="14">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E26" s="15">
-        <v>16.666666666666</v>
+        <v>-20</v>
       </c>
       <c r="F26" s="14">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="G26" s="14">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="H26" s="15">
-        <v>18.181818181818</v>
+        <v>-9.803921568627</v>
       </c>
       <c r="I26" s="14">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="J26" s="14">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="K26" s="15">
-        <v>12.903225806451</v>
+        <v>10.447761194029</v>
       </c>
       <c r="L26" s="15">
-        <v>-11.392405063291</v>
+        <v>-14.450867052023</v>
       </c>
       <c r="M26" s="15">
-        <v>-13.580246913580</v>
+        <v>-15.909090909090</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,29 +1387,29 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="D27" s="14">
+        <v>3</v>
+      </c>
+      <c r="E27" s="15">
+        <v>-100</v>
       </c>
       <c r="F27" s="14">
         <v>2</v>
       </c>
       <c r="G27" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H27" s="15">
-        <v>0</v>
+        <v>-60</v>
       </c>
       <c r="I27" s="14">
         <v>4</v>
       </c>
       <c r="J27" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K27" s="15">
-        <v>0</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="L27" s="15">
         <v>-20</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
+        <v>2</v>
+      </c>
+      <c r="D28" s="14">
         <v>1</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="E28" s="15">
+        <v>100</v>
       </c>
       <c r="F28" s="14">
+        <v>4</v>
+      </c>
+      <c r="G28" s="14">
         <v>3</v>
       </c>
-      <c r="G28" s="14">
-        <v>4</v>
-      </c>
       <c r="H28" s="15">
-        <v>-25</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I28" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J28" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K28" s="15">
-        <v>30</v>
+        <v>36.363636363636</v>
       </c>
       <c r="L28" s="15">
-        <v>0</v>
+        <v>7.142857142857</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1479,7 +1479,7 @@
         <v>20</v>
       </c>
       <c r="G29" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H29" s="15">
         <v>-100</v>
@@ -1500,7 +1500,7 @@
         <v>-87.5</v>
       </c>
       <c r="N29" s="15">
-        <v>-96.296296296296</v>
+        <v>-96.428571428571</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1520,7 +1520,7 @@
         <v>20</v>
       </c>
       <c r="G30" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H30" s="15">
         <v>-100</v>
@@ -1541,7 +1541,7 @@
         <v>-87.5</v>
       </c>
       <c r="N30" s="15">
-        <v>-96.153846153846</v>
+        <v>-96.296296296296</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-023pct.xlsx
+++ b/data/source/weekly/cs-en-us-023pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">14</t>
+      <t xml:space="preserve">15</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/30/2026</t>
+      <t xml:space="preserve">4/6/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/5/2026</t>
+      <t xml:space="preserve">4/12/2026</t>
     </r>
   </si>
   <si>
@@ -895,11 +895,11 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="14">
-        <v>3</v>
-      </c>
-      <c r="E15" s="15">
-        <v>-100</v>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="14">
         <v>2</v>
@@ -926,7 +926,7 @@
         <v>100</v>
       </c>
       <c r="N15" s="15">
-        <v>-77.777777777777</v>
+        <v>-78.947368421052</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D16" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E16" s="15">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="F16" s="14">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G16" s="14">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H16" s="15">
-        <v>-33.333333333333</v>
+        <v>6.666666666666</v>
       </c>
       <c r="I16" s="14">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="J16" s="14">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K16" s="15">
-        <v>-42.1875</v>
+        <v>-35.384615384615</v>
       </c>
       <c r="L16" s="15">
-        <v>-26</v>
+        <v>-25</v>
       </c>
       <c r="M16" s="15">
-        <v>-40.322580645161</v>
+        <v>-37.313432835820</v>
       </c>
       <c r="N16" s="15">
-        <v>-81.951219512195</v>
+        <v>-80.733944954128</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D17" s="14">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E17" s="15">
-        <v>-36.363636363636</v>
+        <v>-20</v>
       </c>
       <c r="F17" s="14">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G17" s="14">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H17" s="15">
-        <v>-40.909090909090</v>
+        <v>-44.186046511627</v>
       </c>
       <c r="I17" s="14">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="J17" s="14">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="K17" s="15">
-        <v>-35.2</v>
+        <v>-34.074074074074</v>
       </c>
       <c r="L17" s="15">
-        <v>-25.688073394495</v>
+        <v>-24.576271186440</v>
       </c>
       <c r="M17" s="15">
-        <v>102.5</v>
+        <v>106.976744186047</v>
       </c>
       <c r="N17" s="15">
-        <v>-45.270270270270</v>
+        <v>-43.312101910828</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
+      <c r="C18" s="14">
+        <v>1</v>
       </c>
       <c r="D18" s="14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E18" s="15">
-        <v>-100</v>
+        <v>-80</v>
       </c>
       <c r="F18" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G18" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H18" s="15">
-        <v>-76.923076923076</v>
+        <v>-86.666666666666</v>
       </c>
       <c r="I18" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J18" s="14">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="K18" s="15">
-        <v>-41.935483870967</v>
+        <v>-47.222222222222</v>
       </c>
       <c r="L18" s="15">
-        <v>-64</v>
+        <v>-64.150943396226</v>
       </c>
       <c r="M18" s="15">
-        <v>5.882352941176</v>
+        <v>11.764705882352</v>
       </c>
       <c r="N18" s="15">
-        <v>-83.333333333333</v>
+        <v>-82.882882882882</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,81 +1057,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D19" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E19" s="15">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F19" s="14">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="G19" s="14">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="H19" s="15">
-        <v>25.806451612903</v>
+        <v>28</v>
       </c>
       <c r="I19" s="14">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="J19" s="14">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="K19" s="15">
-        <v>2.857142857142</v>
+        <v>2.727272727272</v>
       </c>
       <c r="L19" s="15">
-        <v>10.204081632653</v>
+        <v>8.653846153846</v>
       </c>
       <c r="M19" s="15">
-        <v>80</v>
+        <v>82.258064516129</v>
       </c>
       <c r="N19" s="15">
-        <v>-36.470588235294</v>
+        <v>-36.516853932584</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
+      <c r="C20" s="14">
+        <v>1</v>
       </c>
       <c r="D20" s="14">
         <v>1</v>
       </c>
       <c r="E20" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F20" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G20" s="14">
         <v>8</v>
       </c>
       <c r="H20" s="15">
-        <v>-75</v>
+        <v>-62.5</v>
       </c>
       <c r="I20" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J20" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K20" s="15">
-        <v>-37.5</v>
+        <v>-35.294117647058</v>
       </c>
       <c r="L20" s="15">
-        <v>-44.444444444444</v>
+        <v>-38.888888888888</v>
       </c>
       <c r="M20" s="15">
-        <v>100</v>
+        <v>83.333333333333</v>
       </c>
       <c r="N20" s="15">
-        <v>-89.473684210526</v>
+        <v>-88.888888888888</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,48 +1139,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D21" s="17">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E21" s="18">
-        <v>-25</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="F21" s="17">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="G21" s="17">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="H21" s="18">
-        <v>-28.813559322033</v>
+        <v>-28.181818181818</v>
       </c>
       <c r="I21" s="17">
-        <v>258</v>
+        <v>278</v>
       </c>
       <c r="J21" s="17">
-        <v>348</v>
+        <v>370</v>
       </c>
       <c r="K21" s="18">
-        <v>-25.862068965517</v>
+        <v>-24.864864864864</v>
       </c>
       <c r="L21" s="18">
-        <v>-21.580547112462</v>
+        <v>-21.468926553672</v>
       </c>
       <c r="M21" s="18">
-        <v>37.967914438502</v>
+        <v>40.404040404040</v>
       </c>
       <c r="N21" s="18">
-        <v>-65.6</v>
+        <v>-64.720812182741</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
-        <v>1</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1207,7 +1207,7 @@
         <v>200</v>
       </c>
       <c r="L22" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M22" s="15">
         <v>200</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D23" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E23" s="15">
-        <v>-40</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="F23" s="14">
         <v>29</v>
       </c>
       <c r="G23" s="14">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="H23" s="15">
-        <v>-38.297872340425</v>
+        <v>-35.555555555555</v>
       </c>
       <c r="I23" s="14">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="J23" s="14">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="K23" s="15">
-        <v>-24.561403508771</v>
+        <v>-23.577235772357</v>
       </c>
       <c r="L23" s="15">
-        <v>-10.416666666666</v>
+        <v>-7.843137254901</v>
       </c>
       <c r="M23" s="15">
-        <v>72</v>
+        <v>80.769230769230</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D24" s="14">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E24" s="15">
-        <v>-57.142857142857</v>
+        <v>7.692307692307</v>
       </c>
       <c r="F24" s="14">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="G24" s="14">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="H24" s="15">
-        <v>-22.105263157894</v>
+        <v>-24.271844660194</v>
       </c>
       <c r="I24" s="14">
-        <v>242</v>
+        <v>270</v>
       </c>
       <c r="J24" s="14">
-        <v>281</v>
+        <v>307</v>
       </c>
       <c r="K24" s="15">
-        <v>-13.879003558718</v>
+        <v>-12.052117263843</v>
       </c>
       <c r="L24" s="15">
-        <v>21.608040201005</v>
+        <v>23.287671232876</v>
       </c>
       <c r="M24" s="15">
-        <v>64.625850340136</v>
+        <v>75.324675324675</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D25" s="14">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E25" s="15">
-        <v>-66.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="F25" s="14">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G25" s="14">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="H25" s="15">
-        <v>-63.636363636363</v>
+        <v>-63.414634146341</v>
       </c>
       <c r="I25" s="14">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="J25" s="14">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="K25" s="15">
-        <v>-21.649484536082</v>
+        <v>-25.225225225225</v>
       </c>
       <c r="L25" s="15">
-        <v>111.111111111111</v>
+        <v>112.820512820513</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
+        <v>13</v>
+      </c>
+      <c r="D26" s="14">
         <v>8</v>
       </c>
-      <c r="D26" s="14">
-        <v>10</v>
-      </c>
       <c r="E26" s="15">
-        <v>-20</v>
+        <v>62.5</v>
       </c>
       <c r="F26" s="14">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="G26" s="14">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="H26" s="15">
-        <v>-9.803921568627</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="I26" s="14">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="J26" s="14">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="K26" s="15">
-        <v>10.447761194029</v>
+        <v>12.676056338028</v>
       </c>
       <c r="L26" s="15">
-        <v>-14.450867052023</v>
+        <v>-17.525773195876</v>
       </c>
       <c r="M26" s="15">
-        <v>-15.909090909090</v>
+        <v>-12.568306010929</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,20 +1387,20 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="14">
-        <v>3</v>
-      </c>
-      <c r="E27" s="15">
-        <v>-100</v>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="14">
         <v>2</v>
       </c>
       <c r="G27" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H27" s="15">
-        <v>-60</v>
+        <v>-50</v>
       </c>
       <c r="I27" s="14">
         <v>4</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
+        <v>3</v>
+      </c>
+      <c r="D28" s="14">
         <v>2</v>
       </c>
-      <c r="D28" s="14">
-        <v>1</v>
-      </c>
       <c r="E28" s="15">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F28" s="14">
+        <v>7</v>
+      </c>
+      <c r="G28" s="14">
         <v>4</v>
       </c>
-      <c r="G28" s="14">
-        <v>3</v>
-      </c>
       <c r="H28" s="15">
-        <v>33.333333333333</v>
+        <v>75</v>
       </c>
       <c r="I28" s="14">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J28" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K28" s="15">
-        <v>36.363636363636</v>
+        <v>38.461538461538</v>
       </c>
       <c r="L28" s="15">
-        <v>7.142857142857</v>
+        <v>12.5</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1494,10 +1494,10 @@
         <v>-66.666666666666</v>
       </c>
       <c r="L29" s="15">
-        <v>0</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="M29" s="15">
-        <v>-87.5</v>
+        <v>-90</v>
       </c>
       <c r="N29" s="15">
         <v>-96.428571428571</v>
@@ -1535,10 +1535,10 @@
         <v>-66.666666666666</v>
       </c>
       <c r="L30" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="M30" s="15">
-        <v>-87.5</v>
+        <v>-88.888888888888</v>
       </c>
       <c r="N30" s="15">
         <v>-96.296296296296</v>
@@ -1551,29 +1551,29 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
+      <c r="D31" s="14">
+        <v>1</v>
+      </c>
+      <c r="E31" s="15">
+        <v>-100</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H31" s="13" t="s">
-        <v>21</v>
+      <c r="G31" s="14">
+        <v>1</v>
+      </c>
+      <c r="H31" s="15">
+        <v>-100</v>
       </c>
       <c r="I31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="J31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K31" s="13" t="s">
-        <v>21</v>
+      <c r="J31" s="14">
+        <v>1</v>
+      </c>
+      <c r="K31" s="15">
+        <v>-100</v>
       </c>
       <c r="L31" s="13" t="s">
         <v>21</v>
@@ -1634,8 +1634,8 @@
       <c r="K33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L33" s="13" t="s">
-        <v>21</v>
+      <c r="L33" s="15">
+        <v>-100</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-023pct.xlsx
+++ b/data/source/weekly/cs-en-us-023pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">15</t>
+      <t xml:space="preserve">16</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/6/2026</t>
+      <t xml:space="preserve">4/13/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/12/2026</t>
+      <t xml:space="preserve">4/19/2026</t>
     </r>
   </si>
   <si>
@@ -901,14 +901,14 @@
       <c r="E15" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F15" s="14">
-        <v>2</v>
+      <c r="F15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G15" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H15" s="15">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="I15" s="14">
         <v>4</v>
@@ -926,7 +926,7 @@
         <v>100</v>
       </c>
       <c r="N15" s="15">
-        <v>-78.947368421052</v>
+        <v>-80.952380952380</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D16" s="14">
         <v>1</v>
       </c>
       <c r="E16" s="15">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="F16" s="14">
         <v>16</v>
       </c>
       <c r="G16" s="14">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H16" s="15">
-        <v>6.666666666666</v>
+        <v>60</v>
       </c>
       <c r="I16" s="14">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J16" s="14">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K16" s="15">
-        <v>-35.384615384615</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L16" s="15">
-        <v>-25</v>
+        <v>-25.423728813559</v>
       </c>
       <c r="M16" s="15">
-        <v>-37.313432835820</v>
+        <v>-36.231884057971</v>
       </c>
       <c r="N16" s="15">
-        <v>-80.733944954128</v>
+        <v>-81.512605042016</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D17" s="14">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E17" s="15">
-        <v>-20</v>
+        <v>25</v>
       </c>
       <c r="F17" s="14">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G17" s="14">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="H17" s="15">
-        <v>-44.186046511627</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="I17" s="14">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="J17" s="14">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="K17" s="15">
-        <v>-34.074074074074</v>
+        <v>-30.935251798561</v>
       </c>
       <c r="L17" s="15">
-        <v>-24.576271186440</v>
+        <v>-23.809523809523</v>
       </c>
       <c r="M17" s="15">
-        <v>106.976744186047</v>
+        <v>104.255319148936</v>
       </c>
       <c r="N17" s="15">
-        <v>-43.312101910828</v>
+        <v>-42.514970059880</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E18" s="15">
-        <v>-80</v>
+        <v>-50</v>
       </c>
       <c r="F18" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G18" s="14">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H18" s="15">
-        <v>-86.666666666666</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I18" s="14">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J18" s="14">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="K18" s="15">
-        <v>-47.222222222222</v>
+        <v>-47.5</v>
       </c>
       <c r="L18" s="15">
-        <v>-64.150943396226</v>
+        <v>-65</v>
       </c>
       <c r="M18" s="15">
-        <v>11.764705882352</v>
+        <v>16.666666666666</v>
       </c>
       <c r="N18" s="15">
-        <v>-82.882882882882</v>
+        <v>-82.5</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D19" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E19" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F19" s="14">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="G19" s="14">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="H19" s="15">
-        <v>28</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I19" s="14">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="J19" s="14">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="K19" s="15">
-        <v>2.727272727272</v>
+        <v>4.385964912280</v>
       </c>
       <c r="L19" s="15">
-        <v>8.653846153846</v>
+        <v>7.207207207207</v>
       </c>
       <c r="M19" s="15">
-        <v>82.258064516129</v>
+        <v>80.303030303030</v>
       </c>
       <c r="N19" s="15">
-        <v>-36.516853932584</v>
+        <v>-36.363636363636</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D20" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E20" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F20" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G20" s="14">
         <v>8</v>
       </c>
       <c r="H20" s="15">
-        <v>-62.5</v>
+        <v>-50</v>
       </c>
       <c r="I20" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J20" s="14">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K20" s="15">
-        <v>-35.294117647058</v>
+        <v>-35</v>
       </c>
       <c r="L20" s="15">
-        <v>-38.888888888888</v>
+        <v>-31.578947368421</v>
       </c>
       <c r="M20" s="15">
-        <v>83.333333333333</v>
+        <v>44.444444444444</v>
       </c>
       <c r="N20" s="15">
-        <v>-88.888888888888</v>
+        <v>-88.288288288288</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D21" s="17">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E21" s="18">
-        <v>-9.090909090909</v>
+        <v>6.25</v>
       </c>
       <c r="F21" s="17">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G21" s="17">
-        <v>110</v>
+        <v>87</v>
       </c>
       <c r="H21" s="18">
-        <v>-28.181818181818</v>
+        <v>-12.643678160919</v>
       </c>
       <c r="I21" s="17">
-        <v>278</v>
+        <v>297</v>
       </c>
       <c r="J21" s="17">
-        <v>370</v>
+        <v>386</v>
       </c>
       <c r="K21" s="18">
-        <v>-24.864864864864</v>
+        <v>-23.056994818652</v>
       </c>
       <c r="L21" s="18">
-        <v>-21.468926553672</v>
+        <v>-21.842105263157</v>
       </c>
       <c r="M21" s="18">
-        <v>40.404040404040</v>
+        <v>40.094339622641</v>
       </c>
       <c r="N21" s="18">
-        <v>-64.720812182741</v>
+        <v>-65.058823529411</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
+        <v>5</v>
+      </c>
+      <c r="D23" s="14">
         <v>8</v>
       </c>
-      <c r="D23" s="14">
-        <v>9</v>
-      </c>
       <c r="E23" s="15">
-        <v>-11.111111111111</v>
+        <v>-37.5</v>
       </c>
       <c r="F23" s="14">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G23" s="14">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="H23" s="15">
-        <v>-35.555555555555</v>
+        <v>-30.769230769230</v>
       </c>
       <c r="I23" s="14">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="J23" s="14">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="K23" s="15">
-        <v>-23.577235772357</v>
+        <v>-23.664122137404</v>
       </c>
       <c r="L23" s="15">
-        <v>-7.843137254901</v>
+        <v>-8.256880733944</v>
       </c>
       <c r="M23" s="15">
-        <v>80.769230769230</v>
+        <v>75.438596491228</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D24" s="14">
         <v>26</v>
       </c>
       <c r="E24" s="15">
-        <v>7.692307692307</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="F24" s="14">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G24" s="14">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="H24" s="15">
-        <v>-24.271844660194</v>
+        <v>-24.761904761904</v>
       </c>
       <c r="I24" s="14">
-        <v>270</v>
+        <v>293</v>
       </c>
       <c r="J24" s="14">
-        <v>307</v>
+        <v>333</v>
       </c>
       <c r="K24" s="15">
-        <v>-12.052117263843</v>
+        <v>-12.012012012012</v>
       </c>
       <c r="L24" s="15">
-        <v>23.287671232876</v>
+        <v>23.109243697479</v>
       </c>
       <c r="M24" s="15">
-        <v>75.324675324675</v>
+        <v>70.348837209302</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D25" s="14">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E25" s="15">
+        <v>20</v>
+      </c>
+      <c r="F25" s="14">
+        <v>18</v>
+      </c>
+      <c r="G25" s="14">
+        <v>36</v>
+      </c>
+      <c r="H25" s="15">
         <v>-50</v>
       </c>
-      <c r="F25" s="14">
-        <v>15</v>
-      </c>
-      <c r="G25" s="14">
-        <v>41</v>
-      </c>
-      <c r="H25" s="15">
-        <v>-63.414634146341</v>
-      </c>
       <c r="I25" s="14">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="J25" s="14">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="K25" s="15">
-        <v>-25.225225225225</v>
+        <v>-23.275862068965</v>
       </c>
       <c r="L25" s="15">
-        <v>112.820512820513</v>
+        <v>117.073170731707</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D26" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E26" s="15">
-        <v>62.5</v>
+        <v>166.666666666667</v>
       </c>
       <c r="F26" s="14">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="G26" s="14">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="H26" s="15">
-        <v>-7.142857142857</v>
+        <v>36.111111111111</v>
       </c>
       <c r="I26" s="14">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="J26" s="14">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="K26" s="15">
-        <v>12.676056338028</v>
+        <v>18.243243243243</v>
       </c>
       <c r="L26" s="15">
-        <v>-17.525773195876</v>
+        <v>-15.458937198067</v>
       </c>
       <c r="M26" s="15">
-        <v>-12.568306010929</v>
+        <v>-8.854166666666</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1393,14 +1393,14 @@
       <c r="E27" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F27" s="14">
-        <v>2</v>
+      <c r="F27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G27" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H27" s="15">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="I27" s="14">
         <v>4</v>
@@ -1425,32 +1425,32 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
-        <v>3</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D28" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E28" s="15">
-        <v>50</v>
+        <v>-100</v>
       </c>
       <c r="F28" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G28" s="14">
         <v>4</v>
       </c>
       <c r="H28" s="15">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="I28" s="14">
         <v>18</v>
       </c>
       <c r="J28" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K28" s="15">
-        <v>38.461538461538</v>
+        <v>28.571428571428</v>
       </c>
       <c r="L28" s="15">
         <v>12.5</v>
@@ -1478,11 +1478,11 @@
       <c r="F29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G29" s="14">
-        <v>2</v>
-      </c>
-      <c r="H29" s="15">
-        <v>-100</v>
+      <c r="G29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I29" s="14">
         <v>1</v>
@@ -1497,10 +1497,10 @@
         <v>-66.666666666666</v>
       </c>
       <c r="M29" s="15">
-        <v>-90</v>
+        <v>-90.909090909090</v>
       </c>
       <c r="N29" s="15">
-        <v>-96.428571428571</v>
+        <v>-96.666666666666</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1519,11 +1519,11 @@
       <c r="F30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G30" s="14">
-        <v>2</v>
-      </c>
-      <c r="H30" s="15">
-        <v>-100</v>
+      <c r="G30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I30" s="14">
         <v>1</v>
@@ -1538,10 +1538,10 @@
         <v>-50</v>
       </c>
       <c r="M30" s="15">
-        <v>-88.888888888888</v>
+        <v>-90</v>
       </c>
       <c r="N30" s="15">
-        <v>-96.296296296296</v>
+        <v>-96.428571428571</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1551,11 +1551,11 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="14">
-        <v>1</v>
-      </c>
-      <c r="E31" s="15">
-        <v>-100</v>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-023pct.xlsx
+++ b/data/source/weekly/cs-en-us-023pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">16</t>
+      <t xml:space="preserve">17</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/13/2026</t>
+      <t xml:space="preserve">4/20/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/19/2026</t>
+      <t xml:space="preserve">4/26/2026</t>
     </r>
   </si>
   <si>
@@ -920,13 +920,13 @@
         <v>-33.333333333333</v>
       </c>
       <c r="L15" s="15">
-        <v>100</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M15" s="15">
-        <v>100</v>
+        <v>33.333333333333</v>
       </c>
       <c r="N15" s="15">
-        <v>-80.952380952380</v>
+        <v>-81.818181818181</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D16" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E16" s="15">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="F16" s="14">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G16" s="14">
         <v>10</v>
       </c>
       <c r="H16" s="15">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="I16" s="14">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="J16" s="14">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="K16" s="15">
-        <v>-33.333333333333</v>
+        <v>-30</v>
       </c>
       <c r="L16" s="15">
-        <v>-25.423728813559</v>
+        <v>-24.615384615384</v>
       </c>
       <c r="M16" s="15">
-        <v>-36.231884057971</v>
+        <v>-35.526315789473</v>
       </c>
       <c r="N16" s="15">
-        <v>-81.512605042016</v>
+        <v>-80.555555555555</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D17" s="14">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E17" s="15">
-        <v>25</v>
+        <v>-12.5</v>
       </c>
       <c r="F17" s="14">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G17" s="14">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="H17" s="15">
-        <v>-22.222222222222</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="I17" s="14">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="J17" s="14">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="K17" s="15">
-        <v>-30.935251798561</v>
+        <v>-29.931972789115</v>
       </c>
       <c r="L17" s="15">
-        <v>-23.809523809523</v>
+        <v>-23.134328358209</v>
       </c>
       <c r="M17" s="15">
-        <v>104.255319148936</v>
+        <v>94.339622641509</v>
       </c>
       <c r="N17" s="15">
-        <v>-42.514970059880</v>
+        <v>-42.134831460674</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
+        <v>3</v>
+      </c>
+      <c r="D18" s="14">
         <v>2</v>
       </c>
-      <c r="D18" s="14">
-        <v>4</v>
-      </c>
       <c r="E18" s="15">
-        <v>-50</v>
+        <v>50</v>
       </c>
       <c r="F18" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G18" s="14">
         <v>12</v>
       </c>
       <c r="H18" s="15">
-        <v>-66.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="I18" s="14">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J18" s="14">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="K18" s="15">
-        <v>-47.5</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="L18" s="15">
-        <v>-65</v>
+        <v>-61.290322580645</v>
       </c>
       <c r="M18" s="15">
-        <v>16.666666666666</v>
+        <v>33.333333333333</v>
       </c>
       <c r="N18" s="15">
-        <v>-82.5</v>
+        <v>-81.679389312977</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,81 +1057,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D19" s="14">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E19" s="15">
-        <v>50</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="F19" s="14">
         <v>24</v>
       </c>
       <c r="G19" s="14">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H19" s="15">
-        <v>33.333333333333</v>
+        <v>9.090909090909</v>
       </c>
       <c r="I19" s="14">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="J19" s="14">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="K19" s="15">
-        <v>4.385964912280</v>
+        <v>0</v>
       </c>
       <c r="L19" s="15">
-        <v>7.207207207207</v>
+        <v>6.034482758620</v>
       </c>
       <c r="M19" s="15">
-        <v>80.303030303030</v>
+        <v>83.582089552238</v>
       </c>
       <c r="N19" s="15">
-        <v>-36.363636363636</v>
+        <v>-35.9375</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="14">
-        <v>2</v>
+      <c r="C20" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D20" s="14">
         <v>3</v>
       </c>
       <c r="E20" s="15">
-        <v>-33.333333333333</v>
+        <v>-100</v>
       </c>
       <c r="F20" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G20" s="14">
         <v>8</v>
       </c>
       <c r="H20" s="15">
-        <v>-50</v>
+        <v>-62.5</v>
       </c>
       <c r="I20" s="14">
         <v>13</v>
       </c>
       <c r="J20" s="14">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K20" s="15">
-        <v>-35</v>
+        <v>-43.478260869565</v>
       </c>
       <c r="L20" s="15">
         <v>-31.578947368421</v>
       </c>
       <c r="M20" s="15">
-        <v>44.444444444444</v>
+        <v>8.333333333333</v>
       </c>
       <c r="N20" s="15">
-        <v>-88.288288288288</v>
+        <v>-88.983050847457</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D21" s="17">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E21" s="18">
-        <v>6.25</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="F21" s="17">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G21" s="17">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H21" s="18">
-        <v>-12.643678160919</v>
+        <v>-11.363636363636</v>
       </c>
       <c r="I21" s="17">
-        <v>297</v>
+        <v>316</v>
       </c>
       <c r="J21" s="17">
-        <v>386</v>
+        <v>412</v>
       </c>
       <c r="K21" s="18">
-        <v>-23.056994818652</v>
+        <v>-23.300970873786</v>
       </c>
       <c r="L21" s="18">
-        <v>-21.842105263157</v>
+        <v>-21.393034825870</v>
       </c>
       <c r="M21" s="18">
-        <v>40.094339622641</v>
+        <v>37.391304347826</v>
       </c>
       <c r="N21" s="18">
-        <v>-65.058823529411</v>
+        <v>-64.927857935627</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
+        <v>8</v>
+      </c>
+      <c r="D23" s="14">
         <v>5</v>
       </c>
-      <c r="D23" s="14">
-        <v>8</v>
-      </c>
       <c r="E23" s="15">
-        <v>-37.5</v>
+        <v>60</v>
       </c>
       <c r="F23" s="14">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G23" s="14">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H23" s="15">
-        <v>-30.769230769230</v>
+        <v>-12.5</v>
       </c>
       <c r="I23" s="14">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="J23" s="14">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="K23" s="15">
-        <v>-23.664122137404</v>
+        <v>-20.588235294117</v>
       </c>
       <c r="L23" s="15">
-        <v>-8.256880733944</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="M23" s="15">
-        <v>75.438596491228</v>
+        <v>71.428571428571</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="D24" s="14">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="E24" s="15">
-        <v>-15.384615384615</v>
+        <v>0</v>
       </c>
       <c r="F24" s="14">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G24" s="14">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="H24" s="15">
-        <v>-24.761904761904</v>
+        <v>-18.947368421052</v>
       </c>
       <c r="I24" s="14">
-        <v>293</v>
+        <v>307</v>
       </c>
       <c r="J24" s="14">
-        <v>333</v>
+        <v>348</v>
       </c>
       <c r="K24" s="15">
-        <v>-12.012012012012</v>
+        <v>-11.781609195402</v>
       </c>
       <c r="L24" s="15">
-        <v>23.109243697479</v>
+        <v>21.343873517786</v>
       </c>
       <c r="M24" s="15">
-        <v>70.348837209302</v>
+        <v>74.431818181818</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D25" s="14">
         <v>5</v>
       </c>
       <c r="E25" s="15">
-        <v>20</v>
+        <v>-80</v>
       </c>
       <c r="F25" s="14">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G25" s="14">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="H25" s="15">
-        <v>-50</v>
+        <v>-51.515151515151</v>
       </c>
       <c r="I25" s="14">
         <v>89</v>
       </c>
       <c r="J25" s="14">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="K25" s="15">
-        <v>-23.275862068965</v>
+        <v>-26.446280991735</v>
       </c>
       <c r="L25" s="15">
-        <v>117.073170731707</v>
+        <v>89.361702127659</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D26" s="14">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E26" s="15">
-        <v>166.666666666667</v>
+        <v>-46.153846153846</v>
       </c>
       <c r="F26" s="14">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="G26" s="14">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H26" s="15">
-        <v>36.111111111111</v>
+        <v>18.918918918918</v>
       </c>
       <c r="I26" s="14">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="J26" s="14">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="K26" s="15">
-        <v>18.243243243243</v>
+        <v>13.664596273291</v>
       </c>
       <c r="L26" s="15">
-        <v>-15.458937198067</v>
+        <v>-15.277777777777</v>
       </c>
       <c r="M26" s="15">
-        <v>-8.854166666666</v>
+        <v>-10.294117647058</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1412,7 +1412,7 @@
         <v>-42.857142857142</v>
       </c>
       <c r="L27" s="15">
-        <v>-20</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="14">
+        <v>1</v>
       </c>
       <c r="D28" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="F28" s="14">
         <v>6</v>
       </c>
       <c r="G28" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H28" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I28" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J28" s="14">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K28" s="15">
-        <v>28.571428571428</v>
+        <v>18.75</v>
       </c>
       <c r="L28" s="15">
-        <v>12.5</v>
+        <v>11.764705882352</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="14">
+        <v>1</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1475,8 +1475,8 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="13" t="s">
-        <v>20</v>
+      <c r="F29" s="14">
+        <v>1</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1485,30 +1485,30 @@
         <v>21</v>
       </c>
       <c r="I29" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J29" s="14">
         <v>3</v>
       </c>
       <c r="K29" s="15">
-        <v>-66.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L29" s="15">
-        <v>-66.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M29" s="15">
-        <v>-90.909090909090</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="N29" s="15">
-        <v>-96.666666666666</v>
+        <v>-94.117647058823</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="14">
+        <v>1</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1516,8 +1516,8 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="13" t="s">
-        <v>20</v>
+      <c r="F30" s="14">
+        <v>1</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
@@ -1526,22 +1526,22 @@
         <v>21</v>
       </c>
       <c r="I30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J30" s="14">
         <v>3</v>
       </c>
       <c r="K30" s="15">
-        <v>-66.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L30" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="M30" s="15">
-        <v>-90</v>
+        <v>-81.818181818181</v>
       </c>
       <c r="N30" s="15">
-        <v>-96.428571428571</v>
+        <v>-93.548387096774</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-023pct.xlsx
+++ b/data/source/weekly/cs-en-us-023pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">17</t>
+      <t xml:space="preserve">18</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/20/2026</t>
+      <t xml:space="preserve">4/27/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/26/2026</t>
+      <t xml:space="preserve">5/3/2026</t>
     </r>
   </si>
   <si>
@@ -895,17 +895,17 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="D15" s="14">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15">
+        <v>-100</v>
       </c>
       <c r="F15" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G15" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H15" s="15">
         <v>-100</v>
@@ -914,10 +914,10 @@
         <v>4</v>
       </c>
       <c r="J15" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K15" s="15">
-        <v>-33.333333333333</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="L15" s="15">
         <v>33.333333333333</v>
@@ -926,7 +926,7 @@
         <v>33.333333333333</v>
       </c>
       <c r="N15" s="15">
-        <v>-81.818181818181</v>
+        <v>-83.333333333333</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D16" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E16" s="15">
-        <v>25</v>
+        <v>-85.714285714285</v>
       </c>
       <c r="F16" s="14">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G16" s="14">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H16" s="15">
+        <v>-7.692307692307</v>
+      </c>
+      <c r="I16" s="14">
         <v>50</v>
       </c>
-      <c r="I16" s="14">
-        <v>49</v>
-      </c>
       <c r="J16" s="14">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="K16" s="15">
-        <v>-30</v>
+        <v>-35.064935064935</v>
       </c>
       <c r="L16" s="15">
-        <v>-24.615384615384</v>
+        <v>-30.555555555555</v>
       </c>
       <c r="M16" s="15">
-        <v>-35.526315789473</v>
+        <v>-39.759036144578</v>
       </c>
       <c r="N16" s="15">
-        <v>-80.555555555555</v>
+        <v>-81.273408239700</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -984,72 +984,72 @@
         <v>-12.5</v>
       </c>
       <c r="F17" s="14">
+        <v>28</v>
+      </c>
+      <c r="G17" s="14">
         <v>30</v>
       </c>
-      <c r="G17" s="14">
-        <v>33</v>
-      </c>
       <c r="H17" s="15">
-        <v>-9.090909090909</v>
+        <v>-6.666666666666</v>
       </c>
       <c r="I17" s="14">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="J17" s="14">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="K17" s="15">
-        <v>-29.931972789115</v>
+        <v>-29.032258064516</v>
       </c>
       <c r="L17" s="15">
-        <v>-23.134328358209</v>
+        <v>-25.675675675675</v>
       </c>
       <c r="M17" s="15">
-        <v>94.339622641509</v>
+        <v>80.327868852459</v>
       </c>
       <c r="N17" s="15">
-        <v>-42.134831460674</v>
+        <v>-41.798941798941</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="14">
-        <v>3</v>
+      <c r="C18" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D18" s="14">
         <v>2</v>
       </c>
       <c r="E18" s="15">
-        <v>50</v>
+        <v>-100</v>
       </c>
       <c r="F18" s="14">
         <v>6</v>
       </c>
       <c r="G18" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H18" s="15">
-        <v>-50</v>
+        <v>-53.846153846153</v>
       </c>
       <c r="I18" s="14">
         <v>24</v>
       </c>
       <c r="J18" s="14">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K18" s="15">
-        <v>-42.857142857142</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="L18" s="15">
-        <v>-61.290322580645</v>
+        <v>-63.636363636363</v>
       </c>
       <c r="M18" s="15">
         <v>33.333333333333</v>
       </c>
       <c r="N18" s="15">
-        <v>-81.679389312977</v>
+        <v>-82.481751824817</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D19" s="14">
         <v>9</v>
       </c>
       <c r="E19" s="15">
-        <v>-44.444444444444</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="F19" s="14">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G19" s="14">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="H19" s="15">
-        <v>9.090909090909</v>
+        <v>-7.407407407407</v>
       </c>
       <c r="I19" s="14">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="J19" s="14">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="K19" s="15">
-        <v>0</v>
+        <v>0.757575757575</v>
       </c>
       <c r="L19" s="15">
-        <v>6.034482758620</v>
+        <v>8.130081300813</v>
       </c>
       <c r="M19" s="15">
-        <v>83.582089552238</v>
+        <v>92.753623188405</v>
       </c>
       <c r="N19" s="15">
-        <v>-35.9375</v>
+        <v>-33.165829145728</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,7 +1101,7 @@
         <v>20</v>
       </c>
       <c r="D20" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E20" s="15">
         <v>-100</v>
@@ -1119,19 +1119,19 @@
         <v>13</v>
       </c>
       <c r="J20" s="14">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K20" s="15">
-        <v>-43.478260869565</v>
+        <v>-45.833333333333</v>
       </c>
       <c r="L20" s="15">
-        <v>-31.578947368421</v>
+        <v>-35</v>
       </c>
       <c r="M20" s="15">
-        <v>8.333333333333</v>
+        <v>0</v>
       </c>
       <c r="N20" s="15">
-        <v>-88.983050847457</v>
+        <v>-89.344262295082</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D21" s="17">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E21" s="18">
-        <v>-23.076923076923</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="F21" s="17">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="G21" s="17">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="H21" s="18">
-        <v>-11.363636363636</v>
+        <v>-19.565217391304</v>
       </c>
       <c r="I21" s="17">
-        <v>316</v>
+        <v>334</v>
       </c>
       <c r="J21" s="17">
-        <v>412</v>
+        <v>440</v>
       </c>
       <c r="K21" s="18">
-        <v>-23.300970873786</v>
+        <v>-24.090909090909</v>
       </c>
       <c r="L21" s="18">
-        <v>-21.393034825870</v>
+        <v>-23.218390804597</v>
       </c>
       <c r="M21" s="18">
-        <v>37.391304347826</v>
+        <v>34.677419354838</v>
       </c>
       <c r="N21" s="18">
-        <v>-64.927857935627</v>
+        <v>-64.952780692549</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1188,8 +1188,8 @@
       <c r="E22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F22" s="14">
-        <v>1</v>
+      <c r="F22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>20</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D23" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E23" s="15">
-        <v>60</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="F23" s="14">
         <v>28</v>
       </c>
       <c r="G23" s="14">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="H23" s="15">
-        <v>-12.5</v>
+        <v>-3.448275862068</v>
       </c>
       <c r="I23" s="14">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="J23" s="14">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="K23" s="15">
-        <v>-20.588235294117</v>
+        <v>-20.279720279720</v>
       </c>
       <c r="L23" s="15">
-        <v>-7.692307692307</v>
+        <v>-10.236220472440</v>
       </c>
       <c r="M23" s="15">
-        <v>71.428571428571</v>
+        <v>70.149253731343</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D24" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E24" s="15">
-        <v>0</v>
+        <v>31.25</v>
       </c>
       <c r="F24" s="14">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="G24" s="14">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="H24" s="15">
-        <v>-18.947368421052</v>
+        <v>1.204819277108</v>
       </c>
       <c r="I24" s="14">
-        <v>307</v>
+        <v>326</v>
       </c>
       <c r="J24" s="14">
-        <v>348</v>
+        <v>364</v>
       </c>
       <c r="K24" s="15">
-        <v>-11.781609195402</v>
+        <v>-10.439560439560</v>
       </c>
       <c r="L24" s="15">
-        <v>21.343873517786</v>
+        <v>21.189591078066</v>
       </c>
       <c r="M24" s="15">
-        <v>74.431818181818</v>
+        <v>67.179487179487</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D25" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E25" s="15">
-        <v>-80</v>
+        <v>75</v>
       </c>
       <c r="F25" s="14">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G25" s="14">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="H25" s="15">
-        <v>-51.515151515151</v>
+        <v>-25</v>
       </c>
       <c r="I25" s="14">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="J25" s="14">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="K25" s="15">
-        <v>-26.446280991735</v>
+        <v>-22.4</v>
       </c>
       <c r="L25" s="15">
-        <v>89.361702127659</v>
+        <v>94</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D26" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E26" s="15">
-        <v>-46.153846153846</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F26" s="14">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G26" s="14">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H26" s="15">
-        <v>18.918918918918</v>
+        <v>0</v>
       </c>
       <c r="I26" s="14">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="J26" s="14">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="K26" s="15">
-        <v>13.664596273291</v>
+        <v>6.818181818181</v>
       </c>
       <c r="L26" s="15">
-        <v>-15.277777777777</v>
+        <v>-20.675105485232</v>
       </c>
       <c r="M26" s="15">
-        <v>-10.294117647058</v>
+        <v>-14.932126696832</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,17 +1387,17 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="D27" s="14">
+        <v>1</v>
+      </c>
+      <c r="E27" s="15">
+        <v>-100</v>
       </c>
       <c r="F27" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G27" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H27" s="15">
         <v>-100</v>
@@ -1406,10 +1406,10 @@
         <v>4</v>
       </c>
       <c r="J27" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K27" s="15">
-        <v>-42.857142857142</v>
+        <v>-50</v>
       </c>
       <c r="L27" s="15">
         <v>-33.333333333333</v>
@@ -1428,32 +1428,32 @@
       <c r="C28" s="14">
         <v>1</v>
       </c>
-      <c r="D28" s="14">
-        <v>2</v>
-      </c>
-      <c r="E28" s="15">
-        <v>-50</v>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G28" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H28" s="15">
         <v>0</v>
       </c>
       <c r="I28" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J28" s="14">
         <v>16</v>
       </c>
       <c r="K28" s="15">
-        <v>18.75</v>
+        <v>25</v>
       </c>
       <c r="L28" s="15">
-        <v>11.764705882352</v>
+        <v>11.111111111111</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
-        <v>1</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1476,7 +1476,7 @@
         <v>21</v>
       </c>
       <c r="F29" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1485,30 +1485,30 @@
         <v>21</v>
       </c>
       <c r="I29" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J29" s="14">
         <v>3</v>
       </c>
       <c r="K29" s="15">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="L29" s="15">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="M29" s="15">
-        <v>-83.333333333333</v>
+        <v>-78.571428571428</v>
       </c>
       <c r="N29" s="15">
-        <v>-94.117647058823</v>
+        <v>-91.428571428571</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
-        <v>1</v>
+      <c r="C30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1538,10 +1538,10 @@
         <v>0</v>
       </c>
       <c r="M30" s="15">
-        <v>-81.818181818181</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="N30" s="15">
-        <v>-93.548387096774</v>
+        <v>-93.75</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-023pct.xlsx
+++ b/data/source/weekly/cs-en-us-023pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">18</t>
+      <t xml:space="preserve">19</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/27/2026</t>
+      <t xml:space="preserve">5/4/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">5/3/2026</t>
+      <t xml:space="preserve">5/10/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -895,11 +895,11 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="14">
-        <v>1</v>
-      </c>
-      <c r="E15" s="15">
-        <v>-100</v>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="13" t="s">
         <v>20</v>
@@ -923,10 +923,10 @@
         <v>33.333333333333</v>
       </c>
       <c r="M15" s="15">
-        <v>33.333333333333</v>
+        <v>-20</v>
       </c>
       <c r="N15" s="15">
-        <v>-83.333333333333</v>
+        <v>-84</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D16" s="14">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E16" s="15">
-        <v>-85.714285714285</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F16" s="14">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G16" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H16" s="15">
-        <v>-7.692307692307</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I16" s="14">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="J16" s="14">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="K16" s="15">
-        <v>-35.064935064935</v>
+        <v>-33.75</v>
       </c>
       <c r="L16" s="15">
-        <v>-30.555555555555</v>
+        <v>-32.051282051282</v>
       </c>
       <c r="M16" s="15">
-        <v>-39.759036144578</v>
+        <v>-38.372093023255</v>
       </c>
       <c r="N16" s="15">
-        <v>-81.273408239700</v>
+        <v>-81.272084805653</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
+        <v>4</v>
+      </c>
+      <c r="D17" s="14">
         <v>7</v>
       </c>
-      <c r="D17" s="14">
-        <v>8</v>
-      </c>
       <c r="E17" s="15">
-        <v>-12.5</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="F17" s="14">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="G17" s="14">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H17" s="15">
-        <v>-6.666666666666</v>
+        <v>-14.814814814814</v>
       </c>
       <c r="I17" s="14">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="J17" s="14">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="K17" s="15">
-        <v>-29.032258064516</v>
+        <v>-29.629629629629</v>
       </c>
       <c r="L17" s="15">
-        <v>-25.675675675675</v>
+        <v>-26.923076923076</v>
       </c>
       <c r="M17" s="15">
-        <v>80.327868852459</v>
+        <v>72.727272727272</v>
       </c>
       <c r="N17" s="15">
-        <v>-41.798941798941</v>
+        <v>-41.836734693877</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
+      <c r="C18" s="14">
+        <v>2</v>
       </c>
       <c r="D18" s="14">
         <v>2</v>
       </c>
       <c r="E18" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F18" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G18" s="14">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H18" s="15">
-        <v>-53.846153846153</v>
+        <v>-30</v>
       </c>
       <c r="I18" s="14">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J18" s="14">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K18" s="15">
-        <v>-45.454545454545</v>
+        <v>-43.478260869565</v>
       </c>
       <c r="L18" s="15">
-        <v>-63.636363636363</v>
+        <v>-61.764705882352</v>
       </c>
       <c r="M18" s="15">
-        <v>33.333333333333</v>
+        <v>30</v>
       </c>
       <c r="N18" s="15">
-        <v>-82.481751824817</v>
+        <v>-81.944444444444</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,78 +1060,78 @@
         <v>8</v>
       </c>
       <c r="D19" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E19" s="15">
-        <v>-11.111111111111</v>
+        <v>0</v>
       </c>
       <c r="F19" s="14">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G19" s="14">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="H19" s="15">
-        <v>-7.407407407407</v>
+        <v>-3.333333333333</v>
       </c>
       <c r="I19" s="14">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="J19" s="14">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="K19" s="15">
-        <v>0.757575757575</v>
+        <v>2.142857142857</v>
       </c>
       <c r="L19" s="15">
-        <v>8.130081300813</v>
+        <v>7.518796992481</v>
       </c>
       <c r="M19" s="15">
-        <v>92.753623188405</v>
+        <v>83.333333333333</v>
       </c>
       <c r="N19" s="15">
-        <v>-33.165829145728</v>
+        <v>-33.488372093023</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
+      <c r="C20" s="14">
+        <v>4</v>
       </c>
       <c r="D20" s="14">
         <v>1</v>
       </c>
       <c r="E20" s="15">
-        <v>-100</v>
+        <v>300</v>
       </c>
       <c r="F20" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G20" s="14">
         <v>8</v>
       </c>
       <c r="H20" s="15">
-        <v>-62.5</v>
+        <v>-25</v>
       </c>
       <c r="I20" s="14">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="J20" s="14">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K20" s="15">
-        <v>-45.833333333333</v>
+        <v>-32</v>
       </c>
       <c r="L20" s="15">
-        <v>-35</v>
+        <v>-19.047619047619</v>
       </c>
       <c r="M20" s="15">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="N20" s="15">
-        <v>-89.344262295082</v>
+        <v>-86.614173228346</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="D21" s="17">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E21" s="18">
-        <v>-42.857142857142</v>
+        <v>4.761904761904</v>
       </c>
       <c r="F21" s="17">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G21" s="17">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H21" s="18">
-        <v>-19.565217391304</v>
+        <v>-17.582417582417</v>
       </c>
       <c r="I21" s="17">
-        <v>334</v>
+        <v>357</v>
       </c>
       <c r="J21" s="17">
-        <v>440</v>
+        <v>461</v>
       </c>
       <c r="K21" s="18">
-        <v>-24.090909090909</v>
+        <v>-22.559652928416</v>
       </c>
       <c r="L21" s="18">
-        <v>-23.218390804597</v>
+        <v>-22.727272727272</v>
       </c>
       <c r="M21" s="18">
-        <v>34.677419354838</v>
+        <v>31.25</v>
       </c>
       <c r="N21" s="18">
-        <v>-64.952780692549</v>
+        <v>-64.477611940298</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1210,7 +1210,7 @@
         <v>0</v>
       </c>
       <c r="M22" s="15">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
+        <v>8</v>
+      </c>
+      <c r="D23" s="14">
         <v>6</v>
       </c>
-      <c r="D23" s="14">
-        <v>7</v>
-      </c>
       <c r="E23" s="15">
-        <v>-14.285714285714</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F23" s="14">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G23" s="14">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="H23" s="15">
-        <v>-3.448275862068</v>
+        <v>3.846153846153</v>
       </c>
       <c r="I23" s="14">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="J23" s="14">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="K23" s="15">
-        <v>-20.279720279720</v>
+        <v>-18.120805369127</v>
       </c>
       <c r="L23" s="15">
-        <v>-10.236220472440</v>
+        <v>-7.575757575757</v>
       </c>
       <c r="M23" s="15">
-        <v>70.149253731343</v>
+        <v>64.864864864864</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D24" s="14">
         <v>16</v>
       </c>
       <c r="E24" s="15">
-        <v>31.25</v>
+        <v>18.75</v>
       </c>
       <c r="F24" s="14">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="G24" s="14">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="H24" s="15">
-        <v>1.204819277108</v>
+        <v>2.739726027397</v>
       </c>
       <c r="I24" s="14">
-        <v>326</v>
+        <v>345</v>
       </c>
       <c r="J24" s="14">
-        <v>364</v>
+        <v>380</v>
       </c>
       <c r="K24" s="15">
-        <v>-10.439560439560</v>
+        <v>-9.210526315789</v>
       </c>
       <c r="L24" s="15">
-        <v>21.189591078066</v>
+        <v>22.775800711743</v>
       </c>
       <c r="M24" s="15">
-        <v>67.179487179487</v>
+        <v>62.735849056603</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D25" s="14">
         <v>4</v>
       </c>
       <c r="E25" s="15">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F25" s="14">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="G25" s="14">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="H25" s="15">
-        <v>-25</v>
+        <v>-5.555555555555</v>
       </c>
       <c r="I25" s="14">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="J25" s="14">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="K25" s="15">
-        <v>-22.4</v>
+        <v>-21.705426356589</v>
       </c>
       <c r="L25" s="15">
-        <v>94</v>
+        <v>74.137931034482</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="D26" s="14">
         <v>15</v>
       </c>
       <c r="E26" s="15">
-        <v>-66.666666666666</v>
+        <v>20</v>
       </c>
       <c r="F26" s="14">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="G26" s="14">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="H26" s="15">
-        <v>0</v>
+        <v>-2.040816326530</v>
       </c>
       <c r="I26" s="14">
-        <v>188</v>
+        <v>207</v>
       </c>
       <c r="J26" s="14">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="K26" s="15">
-        <v>6.818181818181</v>
+        <v>8.376963350785</v>
       </c>
       <c r="L26" s="15">
-        <v>-20.675105485232</v>
+        <v>-17.529880478087</v>
       </c>
       <c r="M26" s="15">
-        <v>-14.932126696832</v>
+        <v>-11.158798283261</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,11 +1387,11 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="14">
-        <v>1</v>
-      </c>
-      <c r="E27" s="15">
-        <v>-100</v>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="13" t="s">
         <v>20</v>
@@ -1426,7 +1426,7 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D28" s="13" t="s">
         <v>20</v>
@@ -1435,25 +1435,25 @@
         <v>21</v>
       </c>
       <c r="F28" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G28" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H28" s="15">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I28" s="14">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J28" s="14">
         <v>16</v>
       </c>
       <c r="K28" s="15">
-        <v>25</v>
+        <v>37.5</v>
       </c>
       <c r="L28" s="15">
-        <v>11.111111111111</v>
+        <v>10</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1497,7 +1497,7 @@
         <v>0</v>
       </c>
       <c r="M29" s="15">
-        <v>-78.571428571428</v>
+        <v>-80</v>
       </c>
       <c r="N29" s="15">
         <v>-91.428571428571</v>
@@ -1538,7 +1538,7 @@
         <v>0</v>
       </c>
       <c r="M30" s="15">
-        <v>-83.333333333333</v>
+        <v>-84.615384615384</v>
       </c>
       <c r="N30" s="15">
         <v>-93.75</v>
@@ -1560,11 +1560,11 @@
       <c r="F31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G31" s="14">
-        <v>1</v>
-      </c>
-      <c r="H31" s="15">
-        <v>-100</v>
+      <c r="G31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I31" s="13" t="s">
         <v>20</v>
